--- a/Accounts 2026/Salaries Landco 2026/Landco Salaries 2026/03 Salary sheet for Landco.xlsx
+++ b/Accounts 2026/Salaries Landco 2026/Landco Salaries 2026/03 Salary sheet for Landco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrisa\Dropbox\Andrisa\Landco\Accounts 2026\Salaries Landco 2026\Landco Salaries 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\landco\Accounts 2026\Salaries Landco 2026\Landco Salaries 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0F5334-6061-4ED9-B5E9-EFF8D9A49099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787CFE7C-CC84-4F09-B1C8-A0B713DC25BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="499" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="499" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha de salarios" sheetId="1" r:id="rId1"/>
@@ -1868,6 +1868,12 @@
     <xf numFmtId="4" fontId="37" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1877,17 +1883,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2235,85 +2235,85 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A4:JD42"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="5" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="81" style="6" customWidth="1"/>
-    <col min="4" max="5" width="21.44140625" style="236" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="34.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="39.33203125" style="7" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="28.33203125" style="8" hidden="1" customWidth="1"/>
-    <col min="10" max="12" width="28.33203125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="31.6640625" style="9" customWidth="1"/>
-    <col min="15" max="15" width="18.5546875" style="10" customWidth="1"/>
+    <col min="4" max="5" width="21.42578125" style="236" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="34.7109375" style="6" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="39.28515625" style="7" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="28.28515625" style="8" hidden="1" customWidth="1"/>
+    <col min="10" max="12" width="28.28515625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="31.7109375" style="9" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" style="10" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="11" customWidth="1"/>
     <col min="18" max="18" width="17" style="8" customWidth="1"/>
-    <col min="19" max="19" width="14.33203125" style="12" customWidth="1"/>
-    <col min="20" max="20" width="25.109375" style="8" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" style="6" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.44140625" style="6" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" style="6" customWidth="1"/>
-    <col min="24" max="24" width="24.109375" style="6" customWidth="1"/>
-    <col min="25" max="25" width="30.6640625" style="8" customWidth="1"/>
-    <col min="26" max="26" width="29.88671875" style="8" customWidth="1"/>
-    <col min="27" max="27" width="30.44140625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="12" customWidth="1"/>
+    <col min="20" max="20" width="25.140625" style="8" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" style="6" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" style="6" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="24.140625" style="6" customWidth="1"/>
+    <col min="25" max="25" width="30.7109375" style="8" customWidth="1"/>
+    <col min="26" max="26" width="29.85546875" style="8" customWidth="1"/>
+    <col min="27" max="27" width="30.42578125" style="8" customWidth="1"/>
     <col min="28" max="28" width="12" style="6" customWidth="1"/>
-    <col min="29" max="29" width="27.5546875" style="8" customWidth="1"/>
-    <col min="30" max="30" width="27.44140625" style="8" customWidth="1"/>
-    <col min="31" max="31" width="27.5546875" style="8" customWidth="1"/>
-    <col min="32" max="32" width="31.44140625" style="8" customWidth="1"/>
-    <col min="33" max="33" width="53.88671875" style="6" customWidth="1"/>
-    <col min="34" max="35" width="30.6640625" style="8" customWidth="1"/>
-    <col min="36" max="36" width="40.5546875" style="123" customWidth="1"/>
+    <col min="29" max="29" width="27.5703125" style="8" customWidth="1"/>
+    <col min="30" max="30" width="27.42578125" style="8" customWidth="1"/>
+    <col min="31" max="31" width="27.5703125" style="8" customWidth="1"/>
+    <col min="32" max="32" width="31.42578125" style="8" customWidth="1"/>
+    <col min="33" max="33" width="53.85546875" style="6" customWidth="1"/>
+    <col min="34" max="35" width="30.7109375" style="8" customWidth="1"/>
+    <col min="36" max="36" width="40.5703125" style="123" customWidth="1"/>
     <col min="37" max="37" width="21" style="13" customWidth="1"/>
     <col min="38" max="38" width="23" style="14" customWidth="1"/>
-    <col min="40" max="264" width="9.109375" style="6"/>
+    <col min="40" max="264" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:39" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="242" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="242"/>
-      <c r="C4" s="242"/>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="242"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="242"/>
-      <c r="AB4" s="242"/>
-      <c r="AC4" s="242"/>
-      <c r="AD4" s="242"/>
-      <c r="AE4" s="242"/>
-      <c r="AF4" s="242"/>
+    <row r="4" spans="1:39" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="244" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="244"/>
+      <c r="C4" s="244"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
+      <c r="AD4" s="244"/>
+      <c r="AE4" s="244"/>
+      <c r="AF4" s="244"/>
       <c r="AG4" s="4"/>
       <c r="AH4" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AI4" s="239"/>
     </row>
-    <row r="5" spans="1:39" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="17"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AI5" s="38"/>
     </row>
-    <row r="6" spans="1:39" ht="33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A6" s="31"/>
       <c r="B6" s="31"/>
       <c r="C6" s="32"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AI6" s="38"/>
     </row>
-    <row r="7" spans="1:39" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A7" s="31"/>
       <c r="B7" s="31"/>
       <c r="C7" s="25"/>
@@ -2450,54 +2450,54 @@
       <c r="AH7" s="38"/>
       <c r="AI7" s="38"/>
     </row>
-    <row r="8" spans="1:39" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="246" t="s">
+    <row r="8" spans="1:39" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="243" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="148"/>
-      <c r="C8" s="246" t="s">
+      <c r="C8" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="245" t="s">
+      <c r="D8" s="242" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="245" t="s">
+      <c r="E8" s="242" t="s">
         <v>152</v>
       </c>
-      <c r="F8" s="246" t="s">
+      <c r="F8" s="243" t="s">
         <v>126</v>
       </c>
       <c r="G8" s="148"/>
-      <c r="H8" s="246" t="s">
+      <c r="H8" s="243" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="246" t="s">
+      <c r="I8" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="246"/>
-      <c r="K8" s="246"/>
-      <c r="L8" s="246"/>
-      <c r="M8" s="246"/>
-      <c r="N8" s="246"/>
-      <c r="O8" s="246"/>
-      <c r="P8" s="246"/>
-      <c r="Q8" s="246"/>
-      <c r="R8" s="246"/>
-      <c r="S8" s="246"/>
-      <c r="T8" s="246"/>
-      <c r="U8" s="246"/>
-      <c r="V8" s="246"/>
-      <c r="W8" s="246"/>
-      <c r="X8" s="246"/>
-      <c r="Y8" s="246"/>
+      <c r="J8" s="243"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="243"/>
+      <c r="M8" s="243"/>
+      <c r="N8" s="243"/>
+      <c r="O8" s="243"/>
+      <c r="P8" s="243"/>
+      <c r="Q8" s="243"/>
+      <c r="R8" s="243"/>
+      <c r="S8" s="243"/>
+      <c r="T8" s="243"/>
+      <c r="U8" s="243"/>
+      <c r="V8" s="243"/>
+      <c r="W8" s="243"/>
+      <c r="X8" s="243"/>
+      <c r="Y8" s="243"/>
       <c r="Z8" s="148"/>
-      <c r="AA8" s="246" t="s">
+      <c r="AA8" s="243" t="s">
         <v>15</v>
       </c>
-      <c r="AB8" s="246"/>
-      <c r="AC8" s="246"/>
-      <c r="AD8" s="246"/>
-      <c r="AE8" s="246"/>
+      <c r="AB8" s="243"/>
+      <c r="AC8" s="243"/>
+      <c r="AD8" s="243"/>
+      <c r="AE8" s="243"/>
       <c r="AF8" s="149"/>
       <c r="AG8" s="150"/>
       <c r="AH8" s="149"/>
@@ -2506,17 +2506,17 @@
       <c r="AK8" s="13"/>
       <c r="AL8" s="14"/>
     </row>
-    <row r="9" spans="1:39" s="6" customFormat="1" ht="279.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="246"/>
+    <row r="9" spans="1:39" s="6" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="243"/>
       <c r="B9" s="148"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="246"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="243"/>
       <c r="G9" s="148" t="s">
         <v>129</v>
       </c>
-      <c r="H9" s="246"/>
+      <c r="H9" s="243"/>
       <c r="I9" s="151" t="s">
         <v>123</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="AG9" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="AH9" s="149" t="s">
+      <c r="AH9" s="158" t="s">
         <v>36</v>
       </c>
       <c r="AI9" s="240"/>
@@ -2600,7 +2600,7 @@
       <c r="AK9" s="41"/>
       <c r="AL9" s="14"/>
     </row>
-    <row r="10" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="159">
         <v>1</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="AL10" s="48"/>
       <c r="AM10" s="49"/>
     </row>
-    <row r="11" spans="1:39" s="54" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" s="54" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="159">
         <f>+A10+1</f>
         <v>2</v>
@@ -2816,7 +2816,7 @@
       <c r="AL11" s="52"/>
       <c r="AM11" s="53"/>
     </row>
-    <row r="12" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="159">
         <f t="shared" ref="A12:A30" si="9">+A11+1</f>
         <v>3</v>
@@ -2922,7 +2922,7 @@
       <c r="AL12" s="48"/>
       <c r="AM12" s="49"/>
     </row>
-    <row r="13" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="159">
         <f t="shared" si="9"/>
         <v>4</v>
@@ -3028,7 +3028,7 @@
       <c r="AL13" s="48"/>
       <c r="AM13" s="49"/>
     </row>
-    <row r="14" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="159">
         <f t="shared" si="9"/>
         <v>5</v>
@@ -3132,7 +3132,7 @@
       <c r="AL14" s="48"/>
       <c r="AM14" s="49"/>
     </row>
-    <row r="15" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="159">
         <f t="shared" si="9"/>
         <v>6</v>
@@ -3238,7 +3238,7 @@
       <c r="AL15" s="48"/>
       <c r="AM15" s="49"/>
     </row>
-    <row r="16" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="159">
         <f t="shared" si="9"/>
         <v>7</v>
@@ -3342,7 +3342,7 @@
       <c r="AL16" s="48"/>
       <c r="AM16" s="49"/>
     </row>
-    <row r="17" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="159">
         <f t="shared" si="9"/>
         <v>8</v>
@@ -3446,7 +3446,7 @@
       <c r="AL17" s="48"/>
       <c r="AM17" s="49"/>
     </row>
-    <row r="18" spans="1:180" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:180" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="159">
         <f t="shared" si="9"/>
         <v>9</v>
@@ -3697,7 +3697,7 @@
       <c r="FW18" s="50"/>
       <c r="FX18" s="50"/>
     </row>
-    <row r="19" spans="1:180" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:180" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="159">
         <f t="shared" si="9"/>
         <v>10</v>
@@ -3939,7 +3939,7 @@
       <c r="FW19" s="50"/>
       <c r="FX19" s="50"/>
     </row>
-    <row r="20" spans="1:180" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:180" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="159">
         <f t="shared" si="9"/>
         <v>11</v>
@@ -4040,7 +4040,7 @@
       <c r="AL20" s="48"/>
       <c r="AM20" s="49"/>
     </row>
-    <row r="21" spans="1:180" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:180" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="159">
         <f t="shared" si="9"/>
         <v>12</v>
@@ -4149,7 +4149,7 @@
       <c r="AL21" s="48"/>
       <c r="AM21" s="49"/>
     </row>
-    <row r="22" spans="1:180" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:180" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="159">
         <f t="shared" si="9"/>
         <v>13</v>
@@ -4250,7 +4250,7 @@
       <c r="AL22" s="48"/>
       <c r="AM22" s="49"/>
     </row>
-    <row r="23" spans="1:180" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:180" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="159">
         <f t="shared" si="9"/>
         <v>14</v>
@@ -4351,7 +4351,7 @@
       <c r="AL23" s="48"/>
       <c r="AM23" s="49"/>
     </row>
-    <row r="24" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="159">
         <f t="shared" si="9"/>
         <v>15</v>
@@ -4453,7 +4453,7 @@
       <c r="AK24" s="48"/>
       <c r="AL24" s="49"/>
     </row>
-    <row r="25" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="159">
         <f t="shared" si="9"/>
         <v>16</v>
@@ -4560,7 +4560,7 @@
       <c r="AL25" s="48"/>
       <c r="AM25" s="49"/>
     </row>
-    <row r="26" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="159">
         <f t="shared" si="9"/>
         <v>17</v>
@@ -4661,7 +4661,7 @@
       <c r="AL26" s="48"/>
       <c r="AM26" s="49"/>
     </row>
-    <row r="27" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="159">
         <f t="shared" si="9"/>
         <v>18</v>
@@ -4762,7 +4762,7 @@
       <c r="AL27" s="48"/>
       <c r="AM27" s="49"/>
     </row>
-    <row r="28" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="159">
         <f t="shared" si="9"/>
         <v>19</v>
@@ -4871,7 +4871,7 @@
       <c r="AL28" s="48"/>
       <c r="AM28" s="49"/>
     </row>
-    <row r="29" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:180" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="159">
         <f t="shared" si="9"/>
         <v>20</v>
@@ -4972,7 +4972,7 @@
       <c r="AL29" s="48"/>
       <c r="AM29" s="49"/>
     </row>
-    <row r="30" spans="1:180" s="50" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:180" s="50" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="159">
         <f t="shared" si="9"/>
         <v>21</v>
@@ -5073,7 +5073,7 @@
       <c r="AL30" s="48"/>
       <c r="AM30" s="49"/>
     </row>
-    <row r="31" spans="1:180" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:180" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="195"/>
       <c r="B31" s="195"/>
       <c r="C31" s="196"/>
@@ -5176,7 +5176,7 @@
       <c r="AK31" s="48"/>
       <c r="AL31" s="69"/>
     </row>
-    <row r="32" spans="1:180" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:180" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="200"/>
       <c r="B32" s="200"/>
       <c r="C32" s="201"/>
@@ -5226,7 +5226,7 @@
       <c r="AK32" s="48"/>
       <c r="AL32" s="69"/>
     </row>
-    <row r="33" spans="1:39" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="206"/>
@@ -5266,7 +5266,7 @@
       <c r="AK33" s="48"/>
       <c r="AL33" s="69"/>
     </row>
-    <row r="34" spans="1:39" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="200"/>
       <c r="B34" s="200"/>
       <c r="C34" s="201"/>
@@ -5315,7 +5315,7 @@
       <c r="AK34" s="48"/>
       <c r="AL34" s="69"/>
     </row>
-    <row r="35" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="209"/>
       <c r="B35" s="210"/>
       <c r="C35" s="211"/>
@@ -5356,7 +5356,7 @@
       <c r="AL35" s="85"/>
       <c r="AM35" s="86"/>
     </row>
-    <row r="36" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="76"/>
       <c r="B36" s="77"/>
       <c r="C36" s="88"/>
@@ -5399,7 +5399,7 @@
       <c r="AL36" s="85"/>
       <c r="AM36" s="86"/>
     </row>
-    <row r="37" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="76" t="s">
         <v>72</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="AL37" s="85"/>
       <c r="AM37" s="86"/>
     </row>
-    <row r="38" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="76" t="s">
         <v>75</v>
       </c>
@@ -5493,7 +5493,7 @@
       <c r="AL38" s="85"/>
       <c r="AM38" s="86"/>
     </row>
-    <row r="39" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="76" t="s">
         <v>79</v>
       </c>
@@ -5540,7 +5540,7 @@
       <c r="AL39" s="85"/>
       <c r="AM39" s="86"/>
     </row>
-    <row r="40" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="76" t="s">
         <v>82</v>
       </c>
@@ -5585,7 +5585,7 @@
       <c r="AL40" s="85"/>
       <c r="AM40" s="86"/>
     </row>
-    <row r="41" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="76"/>
       <c r="B41" s="77"/>
       <c r="C41" s="88"/>
@@ -5628,7 +5628,7 @@
       <c r="AL41" s="85"/>
       <c r="AM41" s="86"/>
     </row>
-    <row r="42" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:39" s="87" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="111"/>
       <c r="B42" s="112"/>
       <c r="C42" s="113"/>
@@ -5699,40 +5699,40 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW46"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="5" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="86" style="6" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="21" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5546875" style="8" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="41.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" style="8" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="40.5546875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5703125" style="8" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="41.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="8" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="40.5703125" style="13" customWidth="1"/>
     <col min="12" max="12" width="21" style="13" customWidth="1"/>
     <col min="13" max="13" width="23" style="14" customWidth="1"/>
-    <col min="15" max="257" width="9.109375" style="6"/>
+    <col min="15" max="257" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="242" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
+    <row r="1" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="244" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="244"/>
+      <c r="C1" s="244"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="244"/>
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
       <c r="I1" s="4"/>
       <c r="J1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17" t="s">
@@ -5749,7 +5749,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:155" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:155" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
       <c r="C3" s="32"/>
@@ -5764,7 +5764,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="31"/>
       <c r="B4" s="31"/>
       <c r="C4" s="25"/>
@@ -5776,19 +5776,19 @@
       <c r="I4" s="17"/>
       <c r="J4" s="38"/>
     </row>
-    <row r="5" spans="1:155" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="243" t="s">
+    <row r="5" spans="1:155" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="245" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="243" t="s">
+      <c r="C5" s="245" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="243"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
       <c r="G5" s="39"/>
-      <c r="H5" s="244" t="s">
+      <c r="H5" s="246" t="s">
         <v>16</v>
       </c>
       <c r="I5" s="2"/>
@@ -5797,10 +5797,10 @@
       <c r="L5" s="13"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:155" s="6" customFormat="1" ht="279.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="243"/>
+    <row r="6" spans="1:155" s="6" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="245"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="243"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="39" t="s">
         <v>29</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="G6" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="244"/>
+      <c r="H6" s="246"/>
       <c r="I6" s="2"/>
       <c r="J6" s="39" t="s">
         <v>36</v>
@@ -5822,7 +5822,7 @@
       <c r="L6" s="41"/>
       <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="42">
         <v>1</v>
       </c>
@@ -5864,7 +5864,7 @@
       <c r="M7" s="48"/>
       <c r="N7" s="49"/>
     </row>
-    <row r="8" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="42">
         <f>+A7+1</f>
         <v>2</v>
@@ -5904,7 +5904,7 @@
       <c r="M8" s="48"/>
       <c r="N8" s="49"/>
     </row>
-    <row r="9" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42">
         <f t="shared" ref="A9:A27" si="3">+A8+1</f>
         <v>3</v>
@@ -5944,7 +5944,7 @@
       <c r="M9" s="48"/>
       <c r="N9" s="49"/>
     </row>
-    <row r="10" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -5984,7 +5984,7 @@
       <c r="M10" s="48"/>
       <c r="N10" s="49"/>
     </row>
-    <row r="11" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="42">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -6024,7 +6024,7 @@
       <c r="M11" s="48"/>
       <c r="N11" s="49"/>
     </row>
-    <row r="12" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -6064,7 +6064,7 @@
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
     </row>
-    <row r="13" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -6245,7 +6245,7 @@
       <c r="EX13" s="50"/>
       <c r="EY13" s="50"/>
     </row>
-    <row r="14" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="42">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -6413,7 +6413,7 @@
       <c r="EX14" s="50"/>
       <c r="EY14" s="50"/>
     </row>
-    <row r="15" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -6597,7 +6597,7 @@
       <c r="EX15" s="50"/>
       <c r="EY15" s="50"/>
     </row>
-    <row r="16" spans="1:155" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:155" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -6637,7 +6637,7 @@
       <c r="M16" s="48"/>
       <c r="N16" s="49"/>
     </row>
-    <row r="17" spans="1:14" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="42">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -6677,7 +6677,7 @@
       <c r="M17" s="48"/>
       <c r="N17" s="49"/>
     </row>
-    <row r="18" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -6720,7 +6720,7 @@
       <c r="M18" s="48"/>
       <c r="N18" s="49"/>
     </row>
-    <row r="19" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -6760,7 +6760,7 @@
       <c r="M19" s="48"/>
       <c r="N19" s="49"/>
     </row>
-    <row r="20" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="42">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -6799,7 +6799,7 @@
       <c r="L20" s="48"/>
       <c r="M20" s="49"/>
     </row>
-    <row r="21" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -6839,7 +6839,7 @@
       <c r="M21" s="48"/>
       <c r="N21" s="49"/>
     </row>
-    <row r="22" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="42">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -6879,7 +6879,7 @@
       <c r="M22" s="48"/>
       <c r="N22" s="49"/>
     </row>
-    <row r="23" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="42">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -6922,7 +6922,7 @@
       <c r="M23" s="48"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="42">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -6962,7 +6962,7 @@
       <c r="M24" s="48"/>
       <c r="N24" s="49"/>
     </row>
-    <row r="25" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="42">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -7005,7 +7005,7 @@
       <c r="M25" s="48"/>
       <c r="N25" s="49"/>
     </row>
-    <row r="26" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="42">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -7045,7 +7045,7 @@
       <c r="M26" s="48"/>
       <c r="N26" s="49"/>
     </row>
-    <row r="27" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="42">
         <f t="shared" si="3"/>
         <v>21</v>
@@ -7085,7 +7085,7 @@
       <c r="M27" s="48"/>
       <c r="N27" s="49"/>
     </row>
-    <row r="28" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="141"/>
       <c r="B28" s="141"/>
       <c r="C28" s="142"/>
@@ -7101,7 +7101,7 @@
       <c r="M28" s="48"/>
       <c r="N28" s="49"/>
     </row>
-    <row r="29" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="65"/>
       <c r="B29" s="65"/>
       <c r="C29" s="1" t="s">
@@ -7136,7 +7136,7 @@
       <c r="L29" s="48"/>
       <c r="M29" s="69"/>
     </row>
-    <row r="30" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="71"/>
       <c r="B30" s="71"/>
       <c r="C30" s="72"/>
@@ -7151,7 +7151,7 @@
       <c r="L30" s="48"/>
       <c r="M30" s="69"/>
     </row>
-    <row r="31" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="71"/>
       <c r="B31" s="71"/>
       <c r="C31" s="72"/>
@@ -7166,7 +7166,7 @@
       <c r="L31" s="48"/>
       <c r="M31" s="69"/>
     </row>
-    <row r="32" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="76"/>
       <c r="B32" s="77"/>
       <c r="C32" s="78"/>
@@ -7182,7 +7182,7 @@
       <c r="M32" s="85"/>
       <c r="N32" s="86"/>
     </row>
-    <row r="33" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="76"/>
       <c r="B33" s="77"/>
       <c r="C33" s="88"/>
@@ -7200,7 +7200,7 @@
       <c r="M33" s="85"/>
       <c r="N33" s="86"/>
     </row>
-    <row r="34" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="76" t="s">
         <v>72</v>
       </c>
@@ -7220,7 +7220,7 @@
       <c r="M34" s="85"/>
       <c r="N34" s="86"/>
     </row>
-    <row r="35" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="76" t="s">
         <v>75</v>
       </c>
@@ -7242,7 +7242,7 @@
       <c r="M35" s="85"/>
       <c r="N35" s="86"/>
     </row>
-    <row r="36" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="76" t="s">
         <v>79</v>
       </c>
@@ -7262,7 +7262,7 @@
       <c r="M36" s="85"/>
       <c r="N36" s="86"/>
     </row>
-    <row r="37" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="76" t="s">
         <v>82</v>
       </c>
@@ -7284,7 +7284,7 @@
       <c r="M37" s="85"/>
       <c r="N37" s="86"/>
     </row>
-    <row r="38" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="76"/>
       <c r="B38" s="77"/>
       <c r="C38" s="88"/>
@@ -7300,7 +7300,7 @@
       <c r="M38" s="85"/>
       <c r="N38" s="86"/>
     </row>
-    <row r="39" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="111"/>
       <c r="B39" s="112"/>
       <c r="C39" s="113"/>
@@ -7316,7 +7316,7 @@
       <c r="M39" s="85"/>
       <c r="N39" s="86"/>
     </row>
-    <row r="40" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="121"/>
       <c r="B40" s="121"/>
       <c r="C40" s="122"/>
@@ -7328,21 +7328,21 @@
       <c r="I40" s="122"/>
       <c r="J40" s="123"/>
     </row>
-    <row r="41" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H42" s="8" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D45" s="124" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D46" s="124">
         <f>+D29*7%</f>
         <v>23658.311250000002</v>
@@ -7360,50 +7360,50 @@
   <phoneticPr fontId="31" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23611111111111099" right="0" top="0.31527777777777799" bottom="0.31527777777777799" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="36" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="35" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O606"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="0.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="13" width="9.6640625" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="125"/>
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="247"/>
+      <c r="E1" s="247"/>
+      <c r="F1" s="247"/>
+      <c r="G1" s="247"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
-      <c r="J1" s="248" t="s">
+      <c r="J1" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="248"/>
-    </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="247"/>
+      <c r="L1" s="247"/>
+      <c r="M1" s="247"/>
+      <c r="N1" s="247"/>
+      <c r="O1" s="247"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="125"/>
       <c r="B2" s="126"/>
       <c r="C2" s="128"/>
@@ -7420,28 +7420,28 @@
       <c r="N2" s="128"/>
       <c r="O2" s="128"/>
     </row>
-    <row r="3" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="125"/>
-      <c r="B3" s="247" t="s">
+      <c r="B3" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="247"/>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
-      <c r="G3" s="247"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="248"/>
       <c r="H3" s="129"/>
       <c r="I3" s="130"/>
-      <c r="J3" s="247" t="s">
+      <c r="J3" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="M3" s="247"/>
-      <c r="N3" s="247"/>
-      <c r="O3" s="247"/>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="M3" s="248"/>
+      <c r="N3" s="248"/>
+      <c r="O3" s="248"/>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="125"/>
       <c r="B4" s="131">
         <v>1</v>
@@ -7462,7 +7462,7 @@
       <c r="N4" s="132"/>
       <c r="O4" s="132"/>
     </row>
-    <row r="5" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="125"/>
       <c r="B5" s="133" t="s">
         <v>93</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="O5" s="136"/>
     </row>
-    <row r="6" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="125"/>
       <c r="B6" s="133" t="s">
         <v>94</v>
@@ -7519,7 +7519,7 @@
       <c r="M6" s="135"/>
       <c r="O6" s="135"/>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="125"/>
       <c r="B7" s="133" t="s">
         <v>95</v>
@@ -7546,7 +7546,7 @@
       <c r="N7" s="135"/>
       <c r="O7" s="135"/>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="125"/>
       <c r="B8" s="133"/>
       <c r="C8" s="135"/>
@@ -7563,7 +7563,7 @@
       <c r="N8" s="135"/>
       <c r="O8" s="135"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="125"/>
       <c r="B9" s="133" t="s">
         <v>96</v>
@@ -7590,7 +7590,7 @@
         <v>81000.000000000015</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="125"/>
       <c r="B10" s="133" t="s">
         <v>97</v>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="125"/>
       <c r="B11" s="133" t="s">
         <v>98</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="125"/>
       <c r="B12" s="133" t="s">
         <v>99</v>
@@ -7668,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="125"/>
       <c r="B13" s="135"/>
       <c r="C13" s="135"/>
@@ -7695,7 +7695,7 @@
         <v>81000.000000000015</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="125"/>
       <c r="B14" s="135"/>
       <c r="C14" s="135"/>
@@ -7712,7 +7712,7 @@
       <c r="N14" s="135"/>
       <c r="O14" s="138"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="125"/>
       <c r="B15" s="135"/>
       <c r="C15" s="133" t="s">
@@ -7732,7 +7732,7 @@
       <c r="N15" s="135"/>
       <c r="O15" s="138"/>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="125"/>
       <c r="B16" s="135"/>
       <c r="C16" s="135"/>
@@ -7758,7 +7758,7 @@
         <v>10437.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="125"/>
       <c r="B17" s="135"/>
       <c r="C17" s="135"/>
@@ -7784,7 +7784,7 @@
         <v>2430.0000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="125"/>
       <c r="B18" s="135"/>
       <c r="C18" s="135"/>
@@ -7810,7 +7810,7 @@
         <v>810.00000000000011</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="125"/>
       <c r="B19" s="135"/>
       <c r="C19" s="135"/>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="125"/>
       <c r="B20" s="135"/>
       <c r="C20" s="135"/>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="125"/>
       <c r="B21" s="135"/>
       <c r="C21" s="135"/>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="125"/>
       <c r="B22" s="135"/>
       <c r="C22" s="135"/>
@@ -7905,7 +7905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="125"/>
       <c r="B23" s="135"/>
       <c r="C23" s="135"/>
@@ -7931,7 +7931,7 @@
         <v>13677.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="125"/>
       <c r="B24" s="135"/>
       <c r="C24" s="135"/>
@@ -7947,7 +7947,7 @@
       <c r="N24" s="135"/>
       <c r="O24" s="138"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="125"/>
       <c r="B25" s="135"/>
       <c r="C25" s="133" t="s">
@@ -7973,7 +7973,7 @@
         <v>67322.500000000015</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="125"/>
       <c r="B26" s="135"/>
       <c r="C26" s="133"/>
@@ -7990,7 +7990,7 @@
       <c r="N26" s="135"/>
       <c r="O26" s="138"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="125"/>
       <c r="B27" s="135"/>
       <c r="C27" s="135"/>
@@ -8007,7 +8007,7 @@
       <c r="N27" s="135"/>
       <c r="O27" s="138"/>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="125"/>
       <c r="B28" s="135"/>
       <c r="C28" s="135"/>
@@ -8028,7 +8028,7 @@
       <c r="N28" s="135"/>
       <c r="O28" s="138"/>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="125"/>
       <c r="B29" s="135"/>
       <c r="C29" s="135"/>
@@ -8045,28 +8045,28 @@
       <c r="N29" s="135"/>
       <c r="O29" s="138"/>
     </row>
-    <row r="30" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="125"/>
-      <c r="B30" s="248" t="s">
+      <c r="B30" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="248"/>
-      <c r="D30" s="248"/>
-      <c r="E30" s="248"/>
-      <c r="F30" s="248"/>
-      <c r="G30" s="248"/>
+      <c r="C30" s="247"/>
+      <c r="D30" s="247"/>
+      <c r="E30" s="247"/>
+      <c r="F30" s="247"/>
+      <c r="G30" s="247"/>
       <c r="H30" s="127"/>
       <c r="I30" s="127"/>
-      <c r="J30" s="248" t="s">
+      <c r="J30" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="248"/>
-      <c r="L30" s="248"/>
-      <c r="M30" s="248"/>
-      <c r="N30" s="248"/>
-      <c r="O30" s="248"/>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="247"/>
+      <c r="L30" s="247"/>
+      <c r="M30" s="247"/>
+      <c r="N30" s="247"/>
+      <c r="O30" s="247"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="125"/>
       <c r="B31" s="126"/>
       <c r="C31" s="128"/>
@@ -8083,28 +8083,28 @@
       <c r="N31" s="128"/>
       <c r="O31" s="128"/>
     </row>
-    <row r="32" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125"/>
-      <c r="B32" s="247" t="s">
+      <c r="B32" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="247"/>
-      <c r="D32" s="247"/>
-      <c r="E32" s="247"/>
-      <c r="F32" s="247"/>
-      <c r="G32" s="247"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
+      <c r="G32" s="248"/>
       <c r="H32" s="129"/>
       <c r="I32" s="130"/>
-      <c r="J32" s="247" t="s">
+      <c r="J32" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K32" s="247"/>
-      <c r="L32" s="247"/>
-      <c r="M32" s="247"/>
-      <c r="N32" s="247"/>
-      <c r="O32" s="247"/>
-    </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="248"/>
+      <c r="L32" s="248"/>
+      <c r="M32" s="248"/>
+      <c r="N32" s="248"/>
+      <c r="O32" s="248"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="125"/>
       <c r="B33" s="131">
         <f>+B4+1</f>
@@ -8127,7 +8127,7 @@
       <c r="N33" s="132"/>
       <c r="O33" s="132"/>
     </row>
-    <row r="34" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="125"/>
       <c r="B34" s="133" t="s">
         <v>93</v>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="O34" s="136"/>
     </row>
-    <row r="35" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="125"/>
       <c r="B35" s="133" t="s">
         <v>94</v>
@@ -8185,7 +8185,7 @@
       <c r="M35" s="135"/>
       <c r="O35" s="135"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="125"/>
       <c r="B36" s="133" t="s">
         <v>95</v>
@@ -8212,7 +8212,7 @@
       <c r="N36" s="135"/>
       <c r="O36" s="135"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="125"/>
       <c r="B37" s="133"/>
       <c r="C37" s="135"/>
@@ -8229,7 +8229,7 @@
       <c r="N37" s="135"/>
       <c r="O37" s="135"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="125"/>
       <c r="B38" s="133" t="s">
         <v>96</v>
@@ -8256,7 +8256,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="125"/>
       <c r="B39" s="133" t="s">
         <v>97</v>
@@ -8282,7 +8282,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="125"/>
       <c r="B40" s="133" t="s">
         <v>98</v>
@@ -8308,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="125"/>
       <c r="B41" s="133" t="s">
         <v>99</v>
@@ -8335,7 +8335,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="125"/>
       <c r="B42" s="135"/>
       <c r="C42" s="135"/>
@@ -8362,7 +8362,7 @@
         <v>14642.333333333334</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="125"/>
       <c r="B43" s="135"/>
       <c r="C43" s="135"/>
@@ -8379,7 +8379,7 @@
       <c r="N43" s="135"/>
       <c r="O43" s="138"/>
     </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="125"/>
       <c r="B44" s="135"/>
       <c r="C44" s="133" t="s">
@@ -8399,7 +8399,7 @@
       <c r="N44" s="135"/>
       <c r="O44" s="138"/>
     </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="125"/>
       <c r="B45" s="135"/>
       <c r="C45" s="135"/>
@@ -8425,7 +8425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="125"/>
       <c r="B46" s="135"/>
       <c r="C46" s="135"/>
@@ -8451,7 +8451,7 @@
         <v>439.27</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="125"/>
       <c r="B47" s="135"/>
       <c r="C47" s="135"/>
@@ -8477,7 +8477,7 @@
         <v>146.42333333333335</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="125"/>
       <c r="B48" s="135"/>
       <c r="C48" s="135"/>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="125"/>
       <c r="B49" s="135"/>
       <c r="C49" s="135"/>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="125"/>
       <c r="B50" s="135"/>
       <c r="C50" s="135"/>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="125"/>
       <c r="B51" s="135"/>
       <c r="C51" s="135"/>
@@ -8572,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="125"/>
       <c r="B52" s="135"/>
       <c r="C52" s="135"/>
@@ -8598,7 +8598,7 @@
         <v>585.69333333333338</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="125"/>
       <c r="B53" s="135"/>
       <c r="C53" s="135"/>
@@ -8615,7 +8615,7 @@
       <c r="N53" s="135"/>
       <c r="O53" s="138"/>
     </row>
-    <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="125"/>
       <c r="B54" s="135"/>
       <c r="C54" s="133" t="s">
@@ -8642,7 +8642,7 @@
         <v>14056.640000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="125"/>
       <c r="B55" s="135"/>
       <c r="C55" s="133"/>
@@ -8659,7 +8659,7 @@
       <c r="N55" s="135"/>
       <c r="O55" s="138"/>
     </row>
-    <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="125"/>
       <c r="B56" s="135"/>
       <c r="C56" s="135"/>
@@ -8676,7 +8676,7 @@
       <c r="N56" s="135"/>
       <c r="O56" s="138"/>
     </row>
-    <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="125"/>
       <c r="B57" s="135"/>
       <c r="C57" s="135"/>
@@ -8697,7 +8697,7 @@
       <c r="N57" s="135"/>
       <c r="O57" s="138"/>
     </row>
-    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="125"/>
       <c r="B58" s="135"/>
       <c r="C58" s="135"/>
@@ -8714,28 +8714,28 @@
       <c r="N58" s="135"/>
       <c r="O58" s="138"/>
     </row>
-    <row r="59" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="125"/>
-      <c r="B59" s="248" t="s">
+      <c r="B59" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C59" s="248"/>
-      <c r="D59" s="248"/>
-      <c r="E59" s="248"/>
-      <c r="F59" s="248"/>
-      <c r="G59" s="248"/>
+      <c r="C59" s="247"/>
+      <c r="D59" s="247"/>
+      <c r="E59" s="247"/>
+      <c r="F59" s="247"/>
+      <c r="G59" s="247"/>
       <c r="H59" s="127"/>
       <c r="I59" s="127"/>
-      <c r="J59" s="248" t="s">
+      <c r="J59" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K59" s="248"/>
-      <c r="L59" s="248"/>
-      <c r="M59" s="248"/>
-      <c r="N59" s="248"/>
-      <c r="O59" s="248"/>
-    </row>
-    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K59" s="247"/>
+      <c r="L59" s="247"/>
+      <c r="M59" s="247"/>
+      <c r="N59" s="247"/>
+      <c r="O59" s="247"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="125"/>
       <c r="B60" s="126"/>
       <c r="C60" s="128"/>
@@ -8752,28 +8752,28 @@
       <c r="N60" s="128"/>
       <c r="O60" s="128"/>
     </row>
-    <row r="61" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="125"/>
-      <c r="B61" s="247" t="s">
+      <c r="B61" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="247"/>
-      <c r="D61" s="247"/>
-      <c r="E61" s="247"/>
-      <c r="F61" s="247"/>
-      <c r="G61" s="247"/>
+      <c r="C61" s="248"/>
+      <c r="D61" s="248"/>
+      <c r="E61" s="248"/>
+      <c r="F61" s="248"/>
+      <c r="G61" s="248"/>
       <c r="H61" s="129"/>
       <c r="I61" s="130"/>
-      <c r="J61" s="247" t="s">
+      <c r="J61" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K61" s="247"/>
-      <c r="L61" s="247"/>
-      <c r="M61" s="247"/>
-      <c r="N61" s="247"/>
-      <c r="O61" s="247"/>
-    </row>
-    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K61" s="248"/>
+      <c r="L61" s="248"/>
+      <c r="M61" s="248"/>
+      <c r="N61" s="248"/>
+      <c r="O61" s="248"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="125"/>
       <c r="B62" s="131">
         <f>+B33+1</f>
@@ -8796,7 +8796,7 @@
       <c r="N62" s="132"/>
       <c r="O62" s="132"/>
     </row>
-    <row r="63" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="125"/>
       <c r="B63" s="133" t="s">
         <v>93</v>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="O63" s="136"/>
     </row>
-    <row r="64" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="125"/>
       <c r="B64" s="133" t="s">
         <v>94</v>
@@ -8854,7 +8854,7 @@
       <c r="M64" s="135"/>
       <c r="O64" s="135"/>
     </row>
-    <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="125"/>
       <c r="B65" s="133" t="s">
         <v>95</v>
@@ -8878,7 +8878,7 @@
       <c r="N65" s="135"/>
       <c r="O65" s="135"/>
     </row>
-    <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="125"/>
       <c r="B66" s="133"/>
       <c r="C66" s="135"/>
@@ -8895,7 +8895,7 @@
       <c r="N66" s="135"/>
       <c r="O66" s="135"/>
     </row>
-    <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="125"/>
       <c r="B67" s="133" t="s">
         <v>96</v>
@@ -8922,7 +8922,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="125"/>
       <c r="B68" s="133" t="s">
         <v>97</v>
@@ -8948,7 +8948,7 @@
         <v>944.67</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="125"/>
       <c r="B69" s="133" t="s">
         <v>98</v>
@@ -8974,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="125"/>
       <c r="B70" s="133" t="s">
         <v>99</v>
@@ -9001,7 +9001,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="125"/>
       <c r="B71" s="135"/>
       <c r="C71" s="135"/>
@@ -9028,7 +9028,7 @@
         <v>14170.003333333334</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="125"/>
       <c r="B72" s="135"/>
       <c r="C72" s="135"/>
@@ -9045,7 +9045,7 @@
       <c r="N72" s="135"/>
       <c r="O72" s="138"/>
     </row>
-    <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="125"/>
       <c r="B73" s="135"/>
       <c r="C73" s="133" t="s">
@@ -9065,7 +9065,7 @@
       <c r="N73" s="135"/>
       <c r="O73" s="138"/>
     </row>
-    <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="125"/>
       <c r="B74" s="135"/>
       <c r="C74" s="135"/>
@@ -9091,7 +9091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="125"/>
       <c r="B75" s="135"/>
       <c r="C75" s="135"/>
@@ -9117,7 +9117,7 @@
         <v>425.1001</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="125"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -9143,7 +9143,7 @@
         <v>141.70003333333335</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="125"/>
       <c r="B77" s="135"/>
       <c r="C77" s="135"/>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="125"/>
       <c r="B78" s="135"/>
       <c r="C78" s="135"/>
@@ -9189,7 +9189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="125"/>
       <c r="B79" s="135"/>
       <c r="C79" s="135"/>
@@ -9212,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="125"/>
       <c r="B80" s="135"/>
       <c r="C80" s="135"/>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="125"/>
       <c r="B81" s="135"/>
       <c r="C81" s="135"/>
@@ -9265,7 +9265,7 @@
         <v>566.80013333333341</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="125"/>
       <c r="B82" s="135"/>
       <c r="C82" s="135"/>
@@ -9282,7 +9282,7 @@
       <c r="N82" s="135"/>
       <c r="O82" s="138"/>
     </row>
-    <row r="83" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="125"/>
       <c r="B83" s="135"/>
       <c r="C83" s="133" t="s">
@@ -9309,7 +9309,7 @@
         <v>13603.2032</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="125"/>
       <c r="B84" s="135"/>
       <c r="C84" s="133"/>
@@ -9326,7 +9326,7 @@
       <c r="N84" s="135"/>
       <c r="O84" s="138"/>
     </row>
-    <row r="85" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="125"/>
       <c r="B85" s="135"/>
       <c r="C85" s="135"/>
@@ -9343,7 +9343,7 @@
       <c r="N85" s="135"/>
       <c r="O85" s="138"/>
     </row>
-    <row r="86" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="125"/>
       <c r="B86" s="135"/>
       <c r="C86" s="135"/>
@@ -9364,7 +9364,7 @@
       <c r="N86" s="135"/>
       <c r="O86" s="138"/>
     </row>
-    <row r="87" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="125"/>
       <c r="B87" s="135"/>
       <c r="C87" s="135"/>
@@ -9381,28 +9381,28 @@
       <c r="N87" s="135"/>
       <c r="O87" s="138"/>
     </row>
-    <row r="88" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="125"/>
-      <c r="B88" s="248" t="s">
+      <c r="B88" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C88" s="248"/>
-      <c r="D88" s="248"/>
-      <c r="E88" s="248"/>
-      <c r="F88" s="248"/>
-      <c r="G88" s="248"/>
+      <c r="C88" s="247"/>
+      <c r="D88" s="247"/>
+      <c r="E88" s="247"/>
+      <c r="F88" s="247"/>
+      <c r="G88" s="247"/>
       <c r="H88" s="127"/>
       <c r="I88" s="127"/>
-      <c r="J88" s="248" t="s">
+      <c r="J88" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K88" s="248"/>
-      <c r="L88" s="248"/>
-      <c r="M88" s="248"/>
-      <c r="N88" s="248"/>
-      <c r="O88" s="248"/>
-    </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K88" s="247"/>
+      <c r="L88" s="247"/>
+      <c r="M88" s="247"/>
+      <c r="N88" s="247"/>
+      <c r="O88" s="247"/>
+    </row>
+    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="125"/>
       <c r="B89" s="126"/>
       <c r="C89" s="128"/>
@@ -9419,28 +9419,28 @@
       <c r="N89" s="128"/>
       <c r="O89" s="128"/>
     </row>
-    <row r="90" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="125"/>
-      <c r="B90" s="247" t="s">
+      <c r="B90" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C90" s="247"/>
-      <c r="D90" s="247"/>
-      <c r="E90" s="247"/>
-      <c r="F90" s="247"/>
-      <c r="G90" s="247"/>
+      <c r="C90" s="248"/>
+      <c r="D90" s="248"/>
+      <c r="E90" s="248"/>
+      <c r="F90" s="248"/>
+      <c r="G90" s="248"/>
       <c r="H90" s="129"/>
       <c r="I90" s="130"/>
-      <c r="J90" s="247" t="s">
+      <c r="J90" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K90" s="247"/>
-      <c r="L90" s="247"/>
-      <c r="M90" s="247"/>
-      <c r="N90" s="247"/>
-      <c r="O90" s="247"/>
-    </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K90" s="248"/>
+      <c r="L90" s="248"/>
+      <c r="M90" s="248"/>
+      <c r="N90" s="248"/>
+      <c r="O90" s="248"/>
+    </row>
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="125"/>
       <c r="B91" s="131">
         <f>+B62+1</f>
@@ -9462,7 +9462,7 @@
       <c r="N91" s="132"/>
       <c r="O91" s="132"/>
     </row>
-    <row r="92" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="125"/>
       <c r="B92" s="133" t="s">
         <v>93</v>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="O92" s="136"/>
     </row>
-    <row r="93" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="125"/>
       <c r="B93" s="133" t="s">
         <v>94</v>
@@ -9520,7 +9520,7 @@
       <c r="M93" s="135"/>
       <c r="O93" s="135"/>
     </row>
-    <row r="94" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="125"/>
       <c r="B94" s="133" t="s">
         <v>95</v>
@@ -9547,7 +9547,7 @@
       <c r="N94" s="135"/>
       <c r="O94" s="135"/>
     </row>
-    <row r="95" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="125"/>
       <c r="B95" s="133"/>
       <c r="C95" s="135"/>
@@ -9564,7 +9564,7 @@
       <c r="N95" s="135"/>
       <c r="O95" s="135"/>
     </row>
-    <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="125"/>
       <c r="B96" s="133" t="s">
         <v>96</v>
@@ -9591,7 +9591,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="125"/>
       <c r="B97" s="133" t="s">
         <v>97</v>
@@ -9617,7 +9617,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="125"/>
       <c r="B98" s="133" t="s">
         <v>98</v>
@@ -9643,7 +9643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="125"/>
       <c r="B99" s="133" t="s">
         <v>99</v>
@@ -9670,7 +9670,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="125"/>
       <c r="B100" s="135"/>
       <c r="C100" s="135"/>
@@ -9697,7 +9697,7 @@
         <v>14642.333333333334</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="125"/>
       <c r="B101" s="135"/>
       <c r="C101" s="135"/>
@@ -9714,7 +9714,7 @@
       <c r="N101" s="135"/>
       <c r="O101" s="138"/>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="125"/>
       <c r="B102" s="135"/>
       <c r="C102" s="133" t="s">
@@ -9734,7 +9734,7 @@
       <c r="M102" s="135"/>
       <c r="O102" s="138"/>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="125"/>
       <c r="B103" s="135"/>
       <c r="C103" s="135"/>
@@ -9760,7 +9760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="125"/>
       <c r="B104" s="135"/>
       <c r="C104" s="135"/>
@@ -9786,7 +9786,7 @@
         <v>439.27</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="125"/>
       <c r="B105" s="135"/>
       <c r="C105" s="135"/>
@@ -9812,7 +9812,7 @@
         <v>146.42333333333335</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="125"/>
       <c r="B106" s="135"/>
       <c r="C106" s="135"/>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="125"/>
       <c r="B107" s="135"/>
       <c r="C107" s="135"/>
@@ -9858,7 +9858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="125"/>
       <c r="B108" s="135"/>
       <c r="C108" s="135"/>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="125"/>
       <c r="B109" s="135"/>
       <c r="C109" s="135"/>
@@ -9908,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="125"/>
       <c r="B110" s="135"/>
       <c r="C110" s="135"/>
@@ -9935,7 +9935,7 @@
         <v>585.69333333333338</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="125"/>
       <c r="B111" s="135"/>
       <c r="C111" s="135"/>
@@ -9952,7 +9952,7 @@
       <c r="N111" s="135"/>
       <c r="O111" s="138"/>
     </row>
-    <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="125"/>
       <c r="B112" s="135"/>
       <c r="C112" s="133" t="s">
@@ -9979,7 +9979,7 @@
         <v>14056.640000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="125"/>
       <c r="B113" s="135"/>
       <c r="C113" s="133"/>
@@ -9996,7 +9996,7 @@
       <c r="N113" s="135"/>
       <c r="O113" s="138"/>
     </row>
-    <row r="114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="125"/>
       <c r="B114" s="135"/>
       <c r="C114" s="135"/>
@@ -10013,7 +10013,7 @@
       <c r="N114" s="135"/>
       <c r="O114" s="138"/>
     </row>
-    <row r="115" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="125"/>
       <c r="B115" s="135"/>
       <c r="C115" s="135"/>
@@ -10034,28 +10034,28 @@
       <c r="N115" s="135"/>
       <c r="O115" s="138"/>
     </row>
-    <row r="116" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="125"/>
-      <c r="B116" s="248" t="s">
+      <c r="B116" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C116" s="248"/>
-      <c r="D116" s="248"/>
-      <c r="E116" s="248"/>
-      <c r="F116" s="248"/>
-      <c r="G116" s="248"/>
+      <c r="C116" s="247"/>
+      <c r="D116" s="247"/>
+      <c r="E116" s="247"/>
+      <c r="F116" s="247"/>
+      <c r="G116" s="247"/>
       <c r="H116" s="127"/>
       <c r="I116" s="127"/>
-      <c r="J116" s="248" t="s">
+      <c r="J116" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K116" s="248"/>
-      <c r="L116" s="248"/>
-      <c r="M116" s="248"/>
-      <c r="N116" s="248"/>
-      <c r="O116" s="248"/>
-    </row>
-    <row r="117" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K116" s="247"/>
+      <c r="L116" s="247"/>
+      <c r="M116" s="247"/>
+      <c r="N116" s="247"/>
+      <c r="O116" s="247"/>
+    </row>
+    <row r="117" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="125"/>
       <c r="B117" s="126"/>
       <c r="C117" s="128"/>
@@ -10072,28 +10072,28 @@
       <c r="N117" s="128"/>
       <c r="O117" s="128"/>
     </row>
-    <row r="118" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="125"/>
-      <c r="B118" s="247" t="s">
+      <c r="B118" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C118" s="247"/>
-      <c r="D118" s="247"/>
-      <c r="E118" s="247"/>
-      <c r="F118" s="247"/>
-      <c r="G118" s="247"/>
+      <c r="C118" s="248"/>
+      <c r="D118" s="248"/>
+      <c r="E118" s="248"/>
+      <c r="F118" s="248"/>
+      <c r="G118" s="248"/>
       <c r="H118" s="129"/>
       <c r="I118" s="130"/>
-      <c r="J118" s="247" t="s">
+      <c r="J118" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K118" s="247"/>
-      <c r="L118" s="247"/>
-      <c r="M118" s="247"/>
-      <c r="N118" s="247"/>
-      <c r="O118" s="247"/>
-    </row>
-    <row r="119" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K118" s="248"/>
+      <c r="L118" s="248"/>
+      <c r="M118" s="248"/>
+      <c r="N118" s="248"/>
+      <c r="O118" s="248"/>
+    </row>
+    <row r="119" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="125"/>
       <c r="B119" s="131">
         <f>+B91+1</f>
@@ -10115,7 +10115,7 @@
       <c r="N119" s="132"/>
       <c r="O119" s="132"/>
     </row>
-    <row r="120" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="125"/>
       <c r="B120" s="133" t="s">
         <v>93</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="O120" s="136"/>
     </row>
-    <row r="121" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="125"/>
       <c r="B121" s="133" t="s">
         <v>94</v>
@@ -10173,7 +10173,7 @@
       <c r="M121" s="135"/>
       <c r="O121" s="135"/>
     </row>
-    <row r="122" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="125"/>
       <c r="B122" s="133" t="s">
         <v>95</v>
@@ -10200,7 +10200,7 @@
       <c r="N122" s="135"/>
       <c r="O122" s="135"/>
     </row>
-    <row r="123" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="125"/>
       <c r="B123" s="133"/>
       <c r="C123" s="135"/>
@@ -10217,7 +10217,7 @@
       <c r="N123" s="135"/>
       <c r="O123" s="135"/>
     </row>
-    <row r="124" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="125"/>
       <c r="B124" s="133" t="s">
         <v>96</v>
@@ -10244,7 +10244,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="125"/>
       <c r="B125" s="133" t="s">
         <v>97</v>
@@ -10271,7 +10271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="125"/>
       <c r="B126" s="133" t="s">
         <v>98</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="125"/>
       <c r="B127" s="133" t="s">
         <v>99</v>
@@ -10322,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="125"/>
       <c r="B128" s="135"/>
       <c r="C128" s="135"/>
@@ -10349,7 +10349,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="125"/>
       <c r="B129" s="135"/>
       <c r="C129" s="135"/>
@@ -10366,7 +10366,7 @@
       <c r="N129" s="135"/>
       <c r="O129" s="138"/>
     </row>
-    <row r="130" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="125"/>
       <c r="B130" s="135"/>
       <c r="C130" s="133" t="s">
@@ -10386,7 +10386,7 @@
       <c r="N130" s="135"/>
       <c r="O130" s="138"/>
     </row>
-    <row r="131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="125"/>
       <c r="B131" s="135"/>
       <c r="C131" s="135"/>
@@ -10412,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="125"/>
       <c r="B132" s="135"/>
       <c r="C132" s="135"/>
@@ -10438,7 +10438,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="125"/>
       <c r="B133" s="135"/>
       <c r="C133" s="135"/>
@@ -10464,7 +10464,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="125"/>
       <c r="B134" s="135"/>
       <c r="C134" s="135"/>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="125"/>
       <c r="B135" s="135"/>
       <c r="C135" s="135"/>
@@ -10510,7 +10510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="125"/>
       <c r="B136" s="135"/>
       <c r="C136" s="135"/>
@@ -10533,7 +10533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="125"/>
       <c r="B137" s="135"/>
       <c r="C137" s="135"/>
@@ -10560,7 +10560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="125"/>
       <c r="B138" s="135"/>
       <c r="C138" s="135"/>
@@ -10581,7 +10581,7 @@
       <c r="N138" s="135"/>
       <c r="O138" s="138"/>
     </row>
-    <row r="139" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="125"/>
       <c r="B139" s="135"/>
       <c r="C139" s="135"/>
@@ -10607,7 +10607,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="125"/>
       <c r="B140" s="135"/>
       <c r="C140" s="135"/>
@@ -10624,7 +10624,7 @@
       <c r="N140" s="135"/>
       <c r="O140" s="138"/>
     </row>
-    <row r="141" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="125"/>
       <c r="B141" s="135"/>
       <c r="C141" s="133" t="s">
@@ -10651,7 +10651,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="125"/>
       <c r="B142" s="135"/>
       <c r="C142" s="133"/>
@@ -10668,7 +10668,7 @@
       <c r="N142" s="135"/>
       <c r="O142" s="138"/>
     </row>
-    <row r="143" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="125"/>
       <c r="B143" s="135"/>
       <c r="C143" s="135"/>
@@ -10685,7 +10685,7 @@
       <c r="N143" s="135"/>
       <c r="O143" s="138"/>
     </row>
-    <row r="144" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="125"/>
       <c r="B144" s="135"/>
       <c r="C144" s="135"/>
@@ -10706,28 +10706,28 @@
       <c r="N144" s="135"/>
       <c r="O144" s="138"/>
     </row>
-    <row r="145" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="125"/>
-      <c r="B145" s="248" t="s">
+      <c r="B145" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C145" s="248"/>
-      <c r="D145" s="248"/>
-      <c r="E145" s="248"/>
-      <c r="F145" s="248"/>
-      <c r="G145" s="248"/>
+      <c r="C145" s="247"/>
+      <c r="D145" s="247"/>
+      <c r="E145" s="247"/>
+      <c r="F145" s="247"/>
+      <c r="G145" s="247"/>
       <c r="H145" s="127"/>
       <c r="I145" s="127"/>
-      <c r="J145" s="248" t="s">
+      <c r="J145" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K145" s="248"/>
-      <c r="L145" s="248"/>
-      <c r="M145" s="248"/>
-      <c r="N145" s="248"/>
-      <c r="O145" s="248"/>
-    </row>
-    <row r="146" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K145" s="247"/>
+      <c r="L145" s="247"/>
+      <c r="M145" s="247"/>
+      <c r="N145" s="247"/>
+      <c r="O145" s="247"/>
+    </row>
+    <row r="146" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="125"/>
       <c r="B146" s="126"/>
       <c r="C146" s="128"/>
@@ -10744,28 +10744,28 @@
       <c r="N146" s="128"/>
       <c r="O146" s="128"/>
     </row>
-    <row r="147" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="125"/>
-      <c r="B147" s="247" t="s">
+      <c r="B147" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C147" s="247"/>
-      <c r="D147" s="247"/>
-      <c r="E147" s="247"/>
-      <c r="F147" s="247"/>
-      <c r="G147" s="247"/>
+      <c r="C147" s="248"/>
+      <c r="D147" s="248"/>
+      <c r="E147" s="248"/>
+      <c r="F147" s="248"/>
+      <c r="G147" s="248"/>
       <c r="H147" s="129"/>
       <c r="I147" s="130"/>
-      <c r="J147" s="247" t="s">
+      <c r="J147" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K147" s="247"/>
-      <c r="L147" s="247"/>
-      <c r="M147" s="247"/>
-      <c r="N147" s="247"/>
-      <c r="O147" s="247"/>
-    </row>
-    <row r="148" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K147" s="248"/>
+      <c r="L147" s="248"/>
+      <c r="M147" s="248"/>
+      <c r="N147" s="248"/>
+      <c r="O147" s="248"/>
+    </row>
+    <row r="148" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="125"/>
       <c r="B148" s="131">
         <f>+B119+1</f>
@@ -10787,7 +10787,7 @@
       <c r="N148" s="132"/>
       <c r="O148" s="132"/>
     </row>
-    <row r="149" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="125"/>
       <c r="B149" s="133" t="s">
         <v>93</v>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="O149" s="136"/>
     </row>
-    <row r="150" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="125"/>
       <c r="B150" s="133" t="s">
         <v>94</v>
@@ -10845,7 +10845,7 @@
       <c r="M150" s="135"/>
       <c r="O150" s="135"/>
     </row>
-    <row r="151" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="125"/>
       <c r="B151" s="133" t="s">
         <v>95</v>
@@ -10872,7 +10872,7 @@
       <c r="N151" s="135"/>
       <c r="O151" s="135"/>
     </row>
-    <row r="152" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="125"/>
       <c r="B152" s="133"/>
       <c r="C152" s="135"/>
@@ -10889,7 +10889,7 @@
       <c r="N152" s="135"/>
       <c r="O152" s="135"/>
     </row>
-    <row r="153" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="125"/>
       <c r="B153" s="133" t="s">
         <v>96</v>
@@ -10916,7 +10916,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="125"/>
       <c r="B154" s="133" t="s">
         <v>97</v>
@@ -10943,7 +10943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="125"/>
       <c r="B155" s="133" t="s">
         <v>98</v>
@@ -10969,7 +10969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="125"/>
       <c r="B156" s="133" t="s">
         <v>99</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="125"/>
       <c r="B157" s="135"/>
       <c r="C157" s="135"/>
@@ -11021,7 +11021,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="158" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="125"/>
       <c r="B158" s="135"/>
       <c r="C158" s="135"/>
@@ -11038,7 +11038,7 @@
       <c r="N158" s="135"/>
       <c r="O158" s="138"/>
     </row>
-    <row r="159" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="125"/>
       <c r="B159" s="135"/>
       <c r="C159" s="133" t="s">
@@ -11058,7 +11058,7 @@
       <c r="N159" s="135"/>
       <c r="O159" s="138"/>
     </row>
-    <row r="160" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="125"/>
       <c r="B160" s="135"/>
       <c r="C160" s="135"/>
@@ -11084,7 +11084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="125"/>
       <c r="B161" s="135"/>
       <c r="C161" s="135"/>
@@ -11110,7 +11110,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="125"/>
       <c r="B162" s="135"/>
       <c r="C162" s="135"/>
@@ -11136,7 +11136,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="125"/>
       <c r="B163" s="135"/>
       <c r="C163" s="135"/>
@@ -11159,7 +11159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="125"/>
       <c r="B164" s="135"/>
       <c r="C164" s="135"/>
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="125"/>
       <c r="B165" s="135"/>
       <c r="C165" s="135"/>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="125"/>
       <c r="B166" s="135"/>
       <c r="C166" s="135"/>
@@ -11232,7 +11232,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="167" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="125"/>
       <c r="B167" s="135"/>
       <c r="C167" s="135"/>
@@ -11258,7 +11258,7 @@
         <v>2757.8</v>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="125"/>
       <c r="B168" s="135"/>
       <c r="C168" s="135"/>
@@ -11275,7 +11275,7 @@
       <c r="N168" s="135"/>
       <c r="O168" s="138"/>
     </row>
-    <row r="169" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="125"/>
       <c r="B169" s="135"/>
       <c r="C169" s="133" t="s">
@@ -11302,7 +11302,7 @@
         <v>8687.2000000000007</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="125"/>
       <c r="B170" s="135"/>
       <c r="C170" s="133"/>
@@ -11319,7 +11319,7 @@
       <c r="N170" s="135"/>
       <c r="O170" s="138"/>
     </row>
-    <row r="171" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="125"/>
       <c r="B171" s="135"/>
       <c r="C171" s="135"/>
@@ -11336,7 +11336,7 @@
       <c r="N171" s="135"/>
       <c r="O171" s="138"/>
     </row>
-    <row r="172" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="125"/>
       <c r="B172" s="135"/>
       <c r="C172" s="135"/>
@@ -11357,28 +11357,28 @@
       <c r="N172" s="135"/>
       <c r="O172" s="138"/>
     </row>
-    <row r="173" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="125"/>
-      <c r="B173" s="248" t="s">
+      <c r="B173" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C173" s="248"/>
-      <c r="D173" s="248"/>
-      <c r="E173" s="248"/>
-      <c r="F173" s="248"/>
-      <c r="G173" s="248"/>
+      <c r="C173" s="247"/>
+      <c r="D173" s="247"/>
+      <c r="E173" s="247"/>
+      <c r="F173" s="247"/>
+      <c r="G173" s="247"/>
       <c r="H173" s="127"/>
       <c r="I173" s="127"/>
-      <c r="J173" s="248" t="s">
+      <c r="J173" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K173" s="248"/>
-      <c r="L173" s="248"/>
-      <c r="M173" s="248"/>
-      <c r="N173" s="248"/>
-      <c r="O173" s="248"/>
-    </row>
-    <row r="174" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K173" s="247"/>
+      <c r="L173" s="247"/>
+      <c r="M173" s="247"/>
+      <c r="N173" s="247"/>
+      <c r="O173" s="247"/>
+    </row>
+    <row r="174" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="125"/>
       <c r="B174" s="126"/>
       <c r="C174" s="128"/>
@@ -11395,28 +11395,28 @@
       <c r="N174" s="128"/>
       <c r="O174" s="128"/>
     </row>
-    <row r="175" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="125"/>
-      <c r="B175" s="247" t="s">
+      <c r="B175" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C175" s="247"/>
-      <c r="D175" s="247"/>
-      <c r="E175" s="247"/>
-      <c r="F175" s="247"/>
-      <c r="G175" s="247"/>
+      <c r="C175" s="248"/>
+      <c r="D175" s="248"/>
+      <c r="E175" s="248"/>
+      <c r="F175" s="248"/>
+      <c r="G175" s="248"/>
       <c r="H175" s="129"/>
       <c r="I175" s="130"/>
-      <c r="J175" s="247" t="s">
+      <c r="J175" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K175" s="247"/>
-      <c r="L175" s="247"/>
-      <c r="M175" s="247"/>
-      <c r="N175" s="247"/>
-      <c r="O175" s="247"/>
-    </row>
-    <row r="176" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K175" s="248"/>
+      <c r="L175" s="248"/>
+      <c r="M175" s="248"/>
+      <c r="N175" s="248"/>
+      <c r="O175" s="248"/>
+    </row>
+    <row r="176" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="125"/>
       <c r="B176" s="131">
         <f>+B148+1</f>
@@ -11439,7 +11439,7 @@
       <c r="N176" s="132"/>
       <c r="O176" s="132"/>
     </row>
-    <row r="177" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="125"/>
       <c r="B177" s="133" t="s">
         <v>93</v>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="O177" s="136"/>
     </row>
-    <row r="178" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="125"/>
       <c r="B178" s="133" t="s">
         <v>94</v>
@@ -11497,7 +11497,7 @@
       <c r="M178" s="135"/>
       <c r="O178" s="135"/>
     </row>
-    <row r="179" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="125"/>
       <c r="B179" s="133" t="s">
         <v>95</v>
@@ -11524,7 +11524,7 @@
       <c r="N179" s="135"/>
       <c r="O179" s="135"/>
     </row>
-    <row r="180" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="125"/>
       <c r="B180" s="133"/>
       <c r="C180" s="135"/>
@@ -11541,7 +11541,7 @@
       <c r="N180" s="135"/>
       <c r="O180" s="135"/>
     </row>
-    <row r="181" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="125"/>
       <c r="B181" s="133" t="s">
         <v>96</v>
@@ -11568,7 +11568,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="125"/>
       <c r="B182" s="133" t="s">
         <v>97</v>
@@ -11595,7 +11595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="125"/>
       <c r="B183" s="133" t="s">
         <v>98</v>
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="125"/>
       <c r="B184" s="133" t="s">
         <v>99</v>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="125"/>
       <c r="B185" s="135"/>
       <c r="C185" s="135"/>
@@ -11675,7 +11675,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="125"/>
       <c r="B186" s="135"/>
       <c r="C186" s="135"/>
@@ -11692,7 +11692,7 @@
       <c r="N186" s="135"/>
       <c r="O186" s="138"/>
     </row>
-    <row r="187" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="125"/>
       <c r="B187" s="135"/>
       <c r="C187" s="133" t="s">
@@ -11712,7 +11712,7 @@
       <c r="M187" s="135"/>
       <c r="O187" s="138"/>
     </row>
-    <row r="188" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="125"/>
       <c r="B188" s="135"/>
       <c r="C188" s="135"/>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="125"/>
       <c r="B189" s="135"/>
       <c r="C189" s="135"/>
@@ -11764,7 +11764,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="125"/>
       <c r="B190" s="135"/>
       <c r="C190" s="135"/>
@@ -11790,7 +11790,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="125"/>
       <c r="B191" s="135"/>
       <c r="C191" s="135"/>
@@ -11813,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="125"/>
       <c r="B192" s="135"/>
       <c r="C192" s="135"/>
@@ -11836,7 +11836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="125"/>
       <c r="B193" s="135"/>
       <c r="C193" s="135"/>
@@ -11859,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="125"/>
       <c r="B194" s="135"/>
       <c r="C194" s="135"/>
@@ -11886,7 +11886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="125"/>
       <c r="B195" s="135"/>
       <c r="C195" s="135"/>
@@ -11907,7 +11907,7 @@
       <c r="N195" s="135"/>
       <c r="O195" s="138"/>
     </row>
-    <row r="196" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="125"/>
       <c r="B196" s="135"/>
       <c r="C196" s="135"/>
@@ -11934,7 +11934,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="125"/>
       <c r="B197" s="135"/>
       <c r="C197" s="135"/>
@@ -11951,7 +11951,7 @@
       <c r="N197" s="135"/>
       <c r="O197" s="138"/>
     </row>
-    <row r="198" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="125"/>
       <c r="B198" s="135"/>
       <c r="C198" s="133" t="s">
@@ -11978,7 +11978,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="125"/>
       <c r="B199" s="135"/>
       <c r="C199" s="133"/>
@@ -11995,7 +11995,7 @@
       <c r="N199" s="135"/>
       <c r="O199" s="138"/>
     </row>
-    <row r="200" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="125"/>
       <c r="B200" s="135"/>
       <c r="C200" s="135"/>
@@ -12012,7 +12012,7 @@
       <c r="N200" s="135"/>
       <c r="O200" s="138"/>
     </row>
-    <row r="201" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="125"/>
       <c r="B201" s="135"/>
       <c r="C201" s="135"/>
@@ -12033,28 +12033,28 @@
       <c r="N201" s="135"/>
       <c r="O201" s="138"/>
     </row>
-    <row r="202" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="125"/>
-      <c r="B202" s="248" t="s">
+      <c r="B202" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C202" s="248"/>
-      <c r="D202" s="248"/>
-      <c r="E202" s="248"/>
-      <c r="F202" s="248"/>
-      <c r="G202" s="248"/>
+      <c r="C202" s="247"/>
+      <c r="D202" s="247"/>
+      <c r="E202" s="247"/>
+      <c r="F202" s="247"/>
+      <c r="G202" s="247"/>
       <c r="H202" s="127"/>
       <c r="I202" s="127"/>
-      <c r="J202" s="248" t="s">
+      <c r="J202" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K202" s="248"/>
-      <c r="L202" s="248"/>
-      <c r="M202" s="248"/>
-      <c r="N202" s="248"/>
-      <c r="O202" s="248"/>
-    </row>
-    <row r="203" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K202" s="247"/>
+      <c r="L202" s="247"/>
+      <c r="M202" s="247"/>
+      <c r="N202" s="247"/>
+      <c r="O202" s="247"/>
+    </row>
+    <row r="203" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="125"/>
       <c r="B203" s="126"/>
       <c r="C203" s="128"/>
@@ -12071,28 +12071,28 @@
       <c r="N203" s="128"/>
       <c r="O203" s="128"/>
     </row>
-    <row r="204" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="125"/>
-      <c r="B204" s="247" t="s">
+      <c r="B204" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C204" s="247"/>
-      <c r="D204" s="247"/>
-      <c r="E204" s="247"/>
-      <c r="F204" s="247"/>
-      <c r="G204" s="247"/>
+      <c r="C204" s="248"/>
+      <c r="D204" s="248"/>
+      <c r="E204" s="248"/>
+      <c r="F204" s="248"/>
+      <c r="G204" s="248"/>
       <c r="H204" s="129"/>
       <c r="I204" s="130"/>
-      <c r="J204" s="247" t="s">
+      <c r="J204" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K204" s="247"/>
-      <c r="L204" s="247"/>
-      <c r="M204" s="247"/>
-      <c r="N204" s="247"/>
-      <c r="O204" s="247"/>
-    </row>
-    <row r="205" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K204" s="248"/>
+      <c r="L204" s="248"/>
+      <c r="M204" s="248"/>
+      <c r="N204" s="248"/>
+      <c r="O204" s="248"/>
+    </row>
+    <row r="205" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="125"/>
       <c r="B205" s="131">
         <f>+'Folha de salarios'!A17</f>
@@ -12115,7 +12115,7 @@
       <c r="N205" s="132"/>
       <c r="O205" s="132"/>
     </row>
-    <row r="206" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="125"/>
       <c r="B206" s="133" t="s">
         <v>93</v>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="O206" s="136"/>
     </row>
-    <row r="207" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="125"/>
       <c r="B207" s="133" t="s">
         <v>94</v>
@@ -12173,7 +12173,7 @@
       <c r="M207" s="135"/>
       <c r="O207" s="135"/>
     </row>
-    <row r="208" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="125"/>
       <c r="B208" s="133" t="s">
         <v>95</v>
@@ -12200,7 +12200,7 @@
       <c r="N208" s="135"/>
       <c r="O208" s="135"/>
     </row>
-    <row r="209" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="125"/>
       <c r="B209" s="133"/>
       <c r="C209" s="135"/>
@@ -12217,7 +12217,7 @@
       <c r="N209" s="135"/>
       <c r="O209" s="135"/>
     </row>
-    <row r="210" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="125"/>
       <c r="B210" s="133" t="s">
         <v>96</v>
@@ -12244,7 +12244,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="125"/>
       <c r="B211" s="133" t="s">
         <v>97</v>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="125"/>
       <c r="B212" s="133" t="s">
         <v>98</v>
@@ -12297,7 +12297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="125"/>
       <c r="B213" s="133" t="s">
         <v>99</v>
@@ -12324,7 +12324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="125"/>
       <c r="B214" s="135"/>
       <c r="C214" s="135"/>
@@ -12351,7 +12351,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="125"/>
       <c r="B215" s="135"/>
       <c r="C215" s="135"/>
@@ -12368,7 +12368,7 @@
       <c r="N215" s="135"/>
       <c r="O215" s="138"/>
     </row>
-    <row r="216" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="125"/>
       <c r="B216" s="135"/>
       <c r="C216" s="133" t="s">
@@ -12388,7 +12388,7 @@
       <c r="N216" s="135"/>
       <c r="O216" s="138"/>
     </row>
-    <row r="217" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="125"/>
       <c r="B217" s="135"/>
       <c r="C217" s="135"/>
@@ -12414,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="125"/>
       <c r="B218" s="135"/>
       <c r="C218" s="135"/>
@@ -12440,7 +12440,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="125"/>
       <c r="B219" s="135"/>
       <c r="C219" s="135"/>
@@ -12466,7 +12466,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="125"/>
       <c r="B220" s="135"/>
       <c r="C220" s="135"/>
@@ -12489,7 +12489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="125"/>
       <c r="B221" s="135"/>
       <c r="C221" s="135"/>
@@ -12512,7 +12512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="125"/>
       <c r="B222" s="135"/>
       <c r="C222" s="135"/>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="125"/>
       <c r="B223" s="135"/>
       <c r="C223" s="135"/>
@@ -12562,7 +12562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="125"/>
       <c r="B224" s="135"/>
       <c r="C224" s="135"/>
@@ -12583,7 +12583,7 @@
       <c r="N224" s="135"/>
       <c r="O224" s="138"/>
     </row>
-    <row r="225" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="125"/>
       <c r="B225" s="135"/>
       <c r="C225" s="135"/>
@@ -12610,7 +12610,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="226" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="125"/>
       <c r="B226" s="135"/>
       <c r="C226" s="135"/>
@@ -12627,7 +12627,7 @@
       <c r="N226" s="135"/>
       <c r="O226" s="138"/>
     </row>
-    <row r="227" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="125"/>
       <c r="B227" s="135"/>
       <c r="C227" s="133" t="s">
@@ -12654,7 +12654,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="228" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="125"/>
       <c r="B228" s="135"/>
       <c r="C228" s="133"/>
@@ -12671,7 +12671,7 @@
       <c r="N228" s="135"/>
       <c r="O228" s="138"/>
     </row>
-    <row r="229" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="125"/>
       <c r="B229" s="135"/>
       <c r="C229" s="135"/>
@@ -12688,7 +12688,7 @@
       <c r="N229" s="135"/>
       <c r="O229" s="138"/>
     </row>
-    <row r="230" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="125"/>
       <c r="B230" s="135"/>
       <c r="C230" s="135"/>
@@ -12709,28 +12709,28 @@
       <c r="N230" s="135"/>
       <c r="O230" s="138"/>
     </row>
-    <row r="231" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="125"/>
-      <c r="B231" s="248" t="s">
+      <c r="B231" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C231" s="248"/>
-      <c r="D231" s="248"/>
-      <c r="E231" s="248"/>
-      <c r="F231" s="248"/>
-      <c r="G231" s="248"/>
+      <c r="C231" s="247"/>
+      <c r="D231" s="247"/>
+      <c r="E231" s="247"/>
+      <c r="F231" s="247"/>
+      <c r="G231" s="247"/>
       <c r="H231" s="127"/>
       <c r="I231" s="127"/>
-      <c r="J231" s="248" t="s">
+      <c r="J231" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K231" s="248"/>
-      <c r="L231" s="248"/>
-      <c r="M231" s="248"/>
-      <c r="N231" s="248"/>
-      <c r="O231" s="248"/>
-    </row>
-    <row r="232" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K231" s="247"/>
+      <c r="L231" s="247"/>
+      <c r="M231" s="247"/>
+      <c r="N231" s="247"/>
+      <c r="O231" s="247"/>
+    </row>
+    <row r="232" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="125"/>
       <c r="B232" s="126"/>
       <c r="C232" s="128"/>
@@ -12747,28 +12747,28 @@
       <c r="N232" s="128"/>
       <c r="O232" s="128"/>
     </row>
-    <row r="233" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="125"/>
-      <c r="B233" s="247" t="s">
+      <c r="B233" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C233" s="247"/>
-      <c r="D233" s="247"/>
-      <c r="E233" s="247"/>
-      <c r="F233" s="247"/>
-      <c r="G233" s="247"/>
+      <c r="C233" s="248"/>
+      <c r="D233" s="248"/>
+      <c r="E233" s="248"/>
+      <c r="F233" s="248"/>
+      <c r="G233" s="248"/>
       <c r="H233" s="129"/>
       <c r="I233" s="130"/>
-      <c r="J233" s="247" t="s">
+      <c r="J233" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K233" s="247"/>
-      <c r="L233" s="247"/>
-      <c r="M233" s="247"/>
-      <c r="N233" s="247"/>
-      <c r="O233" s="247"/>
-    </row>
-    <row r="234" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K233" s="248"/>
+      <c r="L233" s="248"/>
+      <c r="M233" s="248"/>
+      <c r="N233" s="248"/>
+      <c r="O233" s="248"/>
+    </row>
+    <row r="234" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="125"/>
       <c r="B234" s="131">
         <f>+'Folha de salarios'!A18</f>
@@ -12791,7 +12791,7 @@
       <c r="N234" s="132"/>
       <c r="O234" s="132"/>
     </row>
-    <row r="235" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="125"/>
       <c r="B235" s="133" t="s">
         <v>93</v>
@@ -12823,7 +12823,7 @@
       </c>
       <c r="O235" s="136"/>
     </row>
-    <row r="236" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="125"/>
       <c r="B236" s="133" t="s">
         <v>94</v>
@@ -12849,7 +12849,7 @@
       <c r="M236" s="135"/>
       <c r="O236" s="135"/>
     </row>
-    <row r="237" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="125"/>
       <c r="B237" s="133" t="s">
         <v>95</v>
@@ -12875,7 +12875,7 @@
       <c r="N237" s="135"/>
       <c r="O237" s="135"/>
     </row>
-    <row r="238" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="125"/>
       <c r="B238" s="133"/>
       <c r="C238" s="135"/>
@@ -12892,7 +12892,7 @@
       <c r="N238" s="135"/>
       <c r="O238" s="135"/>
     </row>
-    <row r="239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="125"/>
       <c r="B239" s="133" t="s">
         <v>96</v>
@@ -12919,7 +12919,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="240" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="125"/>
       <c r="B240" s="133" t="s">
         <v>97</v>
@@ -12946,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="125"/>
       <c r="B241" s="133" t="s">
         <v>98</v>
@@ -12970,7 +12970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="125"/>
       <c r="B242" s="133" t="s">
         <v>99</v>
@@ -12996,7 +12996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="125"/>
       <c r="B243" s="135"/>
       <c r="C243" s="135"/>
@@ -13023,7 +13023,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="125"/>
       <c r="B244" s="135"/>
       <c r="C244" s="135"/>
@@ -13040,7 +13040,7 @@
       <c r="N244" s="135"/>
       <c r="O244" s="138"/>
     </row>
-    <row r="245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="125"/>
       <c r="B245" s="135"/>
       <c r="C245" s="133" t="s">
@@ -13060,7 +13060,7 @@
       <c r="M245" s="135"/>
       <c r="O245" s="138"/>
     </row>
-    <row r="246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="125"/>
       <c r="B246" s="135"/>
       <c r="C246" s="135"/>
@@ -13086,7 +13086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="125"/>
       <c r="B247" s="135"/>
       <c r="C247" s="135"/>
@@ -13112,7 +13112,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="125"/>
       <c r="B248" s="135"/>
       <c r="C248" s="135"/>
@@ -13138,7 +13138,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="125"/>
       <c r="B249" s="135"/>
       <c r="C249" s="135"/>
@@ -13161,7 +13161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="125"/>
       <c r="B250" s="135"/>
       <c r="C250" s="135"/>
@@ -13184,7 +13184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="125"/>
       <c r="B251" s="135"/>
       <c r="C251" s="135"/>
@@ -13207,7 +13207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="125"/>
       <c r="B252" s="135"/>
       <c r="C252" s="135"/>
@@ -13234,7 +13234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="125"/>
       <c r="B253" s="135"/>
       <c r="C253" s="135"/>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="125"/>
       <c r="B254" s="135"/>
       <c r="C254" s="135"/>
@@ -13287,7 +13287,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="125"/>
       <c r="B255" s="135"/>
       <c r="C255" s="135"/>
@@ -13304,7 +13304,7 @@
       <c r="N255" s="135"/>
       <c r="O255" s="138"/>
     </row>
-    <row r="256" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="125"/>
       <c r="B256" s="135"/>
       <c r="C256" s="133" t="s">
@@ -13331,7 +13331,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="125"/>
       <c r="B257" s="135"/>
       <c r="C257" s="133"/>
@@ -13348,7 +13348,7 @@
       <c r="N257" s="135"/>
       <c r="O257" s="138"/>
     </row>
-    <row r="258" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="125"/>
       <c r="B258" s="135"/>
       <c r="C258" s="135"/>
@@ -13365,7 +13365,7 @@
       <c r="N258" s="135"/>
       <c r="O258" s="138"/>
     </row>
-    <row r="259" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="125"/>
       <c r="B259" s="135"/>
       <c r="C259" s="135"/>
@@ -13386,28 +13386,28 @@
       <c r="N259" s="135"/>
       <c r="O259" s="138"/>
     </row>
-    <row r="260" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="125"/>
-      <c r="B260" s="248" t="s">
+      <c r="B260" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C260" s="248"/>
-      <c r="D260" s="248"/>
-      <c r="E260" s="248"/>
-      <c r="F260" s="248"/>
-      <c r="G260" s="248"/>
+      <c r="C260" s="247"/>
+      <c r="D260" s="247"/>
+      <c r="E260" s="247"/>
+      <c r="F260" s="247"/>
+      <c r="G260" s="247"/>
       <c r="H260" s="127"/>
       <c r="I260" s="127"/>
-      <c r="J260" s="248" t="s">
+      <c r="J260" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K260" s="248"/>
-      <c r="L260" s="248"/>
-      <c r="M260" s="248"/>
-      <c r="N260" s="248"/>
-      <c r="O260" s="248"/>
-    </row>
-    <row r="261" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K260" s="247"/>
+      <c r="L260" s="247"/>
+      <c r="M260" s="247"/>
+      <c r="N260" s="247"/>
+      <c r="O260" s="247"/>
+    </row>
+    <row r="261" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="125"/>
       <c r="B261" s="126"/>
       <c r="C261" s="128"/>
@@ -13424,28 +13424,28 @@
       <c r="N261" s="128"/>
       <c r="O261" s="128"/>
     </row>
-    <row r="262" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="125"/>
-      <c r="B262" s="247" t="s">
+      <c r="B262" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C262" s="247"/>
-      <c r="D262" s="247"/>
-      <c r="E262" s="247"/>
-      <c r="F262" s="247"/>
-      <c r="G262" s="247"/>
+      <c r="C262" s="248"/>
+      <c r="D262" s="248"/>
+      <c r="E262" s="248"/>
+      <c r="F262" s="248"/>
+      <c r="G262" s="248"/>
       <c r="H262" s="129"/>
       <c r="I262" s="130"/>
-      <c r="J262" s="247" t="s">
+      <c r="J262" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K262" s="247"/>
-      <c r="L262" s="247"/>
-      <c r="M262" s="247"/>
-      <c r="N262" s="247"/>
-      <c r="O262" s="247"/>
-    </row>
-    <row r="263" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K262" s="248"/>
+      <c r="L262" s="248"/>
+      <c r="M262" s="248"/>
+      <c r="N262" s="248"/>
+      <c r="O262" s="248"/>
+    </row>
+    <row r="263" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="125"/>
       <c r="B263" s="131">
         <f>+'Folha de salarios'!A19</f>
@@ -13468,7 +13468,7 @@
       <c r="N263" s="132"/>
       <c r="O263" s="132"/>
     </row>
-    <row r="264" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="125"/>
       <c r="B264" s="133" t="s">
         <v>93</v>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="O264" s="136"/>
     </row>
-    <row r="265" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="125"/>
       <c r="B265" s="133" t="s">
         <v>94</v>
@@ -13526,7 +13526,7 @@
       <c r="M265" s="135"/>
       <c r="O265" s="135"/>
     </row>
-    <row r="266" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="125"/>
       <c r="B266" s="133" t="s">
         <v>95</v>
@@ -13553,7 +13553,7 @@
       <c r="N266" s="135"/>
       <c r="O266" s="135"/>
     </row>
-    <row r="267" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="125"/>
       <c r="B267" s="133"/>
       <c r="C267" s="135"/>
@@ -13570,7 +13570,7 @@
       <c r="N267" s="135"/>
       <c r="O267" s="135"/>
     </row>
-    <row r="268" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="125"/>
       <c r="B268" s="133" t="s">
         <v>96</v>
@@ -13597,7 +13597,7 @@
         <v>14824.000000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="125"/>
       <c r="B269" s="133" t="s">
         <v>97</v>
@@ -13624,7 +13624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="125"/>
       <c r="B270" s="133" t="s">
         <v>98</v>
@@ -13650,7 +13650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="125"/>
       <c r="B271" s="133" t="s">
         <v>99</v>
@@ -13677,7 +13677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="125"/>
       <c r="B272" s="135"/>
       <c r="C272" s="135"/>
@@ -13704,7 +13704,7 @@
         <v>14824.000000000002</v>
       </c>
     </row>
-    <row r="273" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="125"/>
       <c r="B273" s="135"/>
       <c r="C273" s="135"/>
@@ -13721,7 +13721,7 @@
       <c r="N273" s="135"/>
       <c r="O273" s="138"/>
     </row>
-    <row r="274" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="125"/>
       <c r="B274" s="135"/>
       <c r="C274" s="133" t="s">
@@ -13741,7 +13741,7 @@
       <c r="M274" s="135"/>
       <c r="O274" s="138"/>
     </row>
-    <row r="275" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="125"/>
       <c r="B275" s="135"/>
       <c r="C275" s="135"/>
@@ -13767,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="125"/>
       <c r="B276" s="135"/>
       <c r="C276" s="135"/>
@@ -13793,7 +13793,7 @@
         <v>444.72</v>
       </c>
     </row>
-    <row r="277" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="125"/>
       <c r="B277" s="135"/>
       <c r="C277" s="135"/>
@@ -13819,7 +13819,7 @@
         <v>148.24</v>
       </c>
     </row>
-    <row r="278" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="125"/>
       <c r="B278" s="135"/>
       <c r="C278" s="135"/>
@@ -13842,7 +13842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="125"/>
       <c r="B279" s="135"/>
       <c r="C279" s="135"/>
@@ -13865,7 +13865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="125"/>
       <c r="B280" s="135"/>
       <c r="C280" s="135"/>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="125"/>
       <c r="B281" s="135"/>
       <c r="C281" s="135"/>
@@ -13915,7 +13915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="125"/>
       <c r="B282" s="135"/>
       <c r="C282" s="135"/>
@@ -13939,7 +13939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="125"/>
       <c r="B283" s="135"/>
       <c r="C283" s="135"/>
@@ -13966,7 +13966,7 @@
         <v>592.96</v>
       </c>
     </row>
-    <row r="284" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="125"/>
       <c r="B284" s="135"/>
       <c r="C284" s="135"/>
@@ -13983,7 +13983,7 @@
       <c r="N284" s="135"/>
       <c r="O284" s="138"/>
     </row>
-    <row r="285" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="125"/>
       <c r="B285" s="135"/>
       <c r="C285" s="133" t="s">
@@ -14010,7 +14010,7 @@
         <v>14231.04</v>
       </c>
     </row>
-    <row r="286" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="125"/>
       <c r="B286" s="135"/>
       <c r="C286" s="133"/>
@@ -14027,7 +14027,7 @@
       <c r="N286" s="135"/>
       <c r="O286" s="138"/>
     </row>
-    <row r="287" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="125"/>
       <c r="B287" s="135"/>
       <c r="C287" s="135"/>
@@ -14044,7 +14044,7 @@
       <c r="N287" s="135"/>
       <c r="O287" s="138"/>
     </row>
-    <row r="288" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="125"/>
       <c r="B288" s="135"/>
       <c r="C288" s="135"/>
@@ -14065,28 +14065,28 @@
       <c r="N288" s="135"/>
       <c r="O288" s="138"/>
     </row>
-    <row r="289" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="125"/>
-      <c r="B289" s="248" t="s">
+      <c r="B289" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C289" s="248"/>
-      <c r="D289" s="248"/>
-      <c r="E289" s="248"/>
-      <c r="F289" s="248"/>
-      <c r="G289" s="248"/>
+      <c r="C289" s="247"/>
+      <c r="D289" s="247"/>
+      <c r="E289" s="247"/>
+      <c r="F289" s="247"/>
+      <c r="G289" s="247"/>
       <c r="H289" s="127"/>
       <c r="I289" s="127"/>
-      <c r="J289" s="248" t="s">
+      <c r="J289" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K289" s="248"/>
-      <c r="L289" s="248"/>
-      <c r="M289" s="248"/>
-      <c r="N289" s="248"/>
-      <c r="O289" s="248"/>
-    </row>
-    <row r="290" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K289" s="247"/>
+      <c r="L289" s="247"/>
+      <c r="M289" s="247"/>
+      <c r="N289" s="247"/>
+      <c r="O289" s="247"/>
+    </row>
+    <row r="290" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="125"/>
       <c r="B290" s="126"/>
       <c r="C290" s="128"/>
@@ -14103,28 +14103,28 @@
       <c r="N290" s="128"/>
       <c r="O290" s="128"/>
     </row>
-    <row r="291" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="125"/>
-      <c r="B291" s="247" t="s">
+      <c r="B291" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C291" s="247"/>
-      <c r="D291" s="247"/>
-      <c r="E291" s="247"/>
-      <c r="F291" s="247"/>
-      <c r="G291" s="247"/>
+      <c r="C291" s="248"/>
+      <c r="D291" s="248"/>
+      <c r="E291" s="248"/>
+      <c r="F291" s="248"/>
+      <c r="G291" s="248"/>
       <c r="H291" s="129"/>
       <c r="I291" s="130"/>
-      <c r="J291" s="247" t="s">
+      <c r="J291" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K291" s="247"/>
-      <c r="L291" s="247"/>
-      <c r="M291" s="247"/>
-      <c r="N291" s="247"/>
-      <c r="O291" s="247"/>
-    </row>
-    <row r="292" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K291" s="248"/>
+      <c r="L291" s="248"/>
+      <c r="M291" s="248"/>
+      <c r="N291" s="248"/>
+      <c r="O291" s="248"/>
+    </row>
+    <row r="292" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="125"/>
       <c r="B292" s="131">
         <f>+B263+1</f>
@@ -14146,7 +14146,7 @@
       <c r="N292" s="132"/>
       <c r="O292" s="132"/>
     </row>
-    <row r="293" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="125"/>
       <c r="B293" s="133" t="s">
         <v>93</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="O293" s="136"/>
     </row>
-    <row r="294" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="125"/>
       <c r="B294" s="133" t="s">
         <v>94</v>
@@ -14204,7 +14204,7 @@
       <c r="M294" s="135"/>
       <c r="O294" s="135"/>
     </row>
-    <row r="295" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="125"/>
       <c r="B295" s="133" t="s">
         <v>95</v>
@@ -14231,7 +14231,7 @@
       <c r="N295" s="135"/>
       <c r="O295" s="135"/>
     </row>
-    <row r="296" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="125"/>
       <c r="B296" s="133"/>
       <c r="C296" s="135"/>
@@ -14248,7 +14248,7 @@
       <c r="N296" s="135"/>
       <c r="O296" s="135"/>
     </row>
-    <row r="297" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="125"/>
       <c r="B297" s="133" t="s">
         <v>96</v>
@@ -14275,7 +14275,7 @@
         <v>14170.000000000002</v>
       </c>
     </row>
-    <row r="298" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="125"/>
       <c r="B298" s="133" t="s">
         <v>97</v>
@@ -14302,7 +14302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="125"/>
       <c r="B299" s="133" t="s">
         <v>98</v>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="125"/>
       <c r="B300" s="133" t="s">
         <v>99</v>
@@ -14353,7 +14353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="125"/>
       <c r="B301" s="135"/>
       <c r="C301" s="135"/>
@@ -14380,7 +14380,7 @@
         <v>14170.000000000002</v>
       </c>
     </row>
-    <row r="302" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="125"/>
       <c r="B302" s="135"/>
       <c r="C302" s="135"/>
@@ -14397,7 +14397,7 @@
       <c r="N302" s="135"/>
       <c r="O302" s="138"/>
     </row>
-    <row r="303" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="125"/>
       <c r="B303" s="135"/>
       <c r="C303" s="133" t="s">
@@ -14417,7 +14417,7 @@
       <c r="M303" s="135"/>
       <c r="O303" s="138"/>
     </row>
-    <row r="304" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="125"/>
       <c r="B304" s="135"/>
       <c r="C304" s="135"/>
@@ -14443,7 +14443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="125"/>
       <c r="B305" s="135"/>
       <c r="C305" s="135"/>
@@ -14469,7 +14469,7 @@
         <v>425.1</v>
       </c>
     </row>
-    <row r="306" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="125"/>
       <c r="B306" s="135"/>
       <c r="C306" s="135"/>
@@ -14495,7 +14495,7 @@
         <v>141.70000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="125"/>
       <c r="B307" s="135"/>
       <c r="C307" s="135"/>
@@ -14518,7 +14518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="125"/>
       <c r="B308" s="135"/>
       <c r="C308" s="135"/>
@@ -14541,7 +14541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="125"/>
       <c r="B309" s="135"/>
       <c r="C309" s="135"/>
@@ -14564,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="125"/>
       <c r="B310" s="135"/>
       <c r="C310" s="135"/>
@@ -14591,7 +14591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="125"/>
       <c r="B311" s="135"/>
       <c r="C311" s="135"/>
@@ -14615,7 +14615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="125"/>
       <c r="B312" s="135"/>
       <c r="C312" s="135"/>
@@ -14642,7 +14642,7 @@
         <v>566.80000000000007</v>
       </c>
     </row>
-    <row r="313" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="125"/>
       <c r="B313" s="135"/>
       <c r="C313" s="135"/>
@@ -14659,7 +14659,7 @@
       <c r="N313" s="135"/>
       <c r="O313" s="138"/>
     </row>
-    <row r="314" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="125"/>
       <c r="B314" s="135"/>
       <c r="C314" s="133" t="s">
@@ -14686,7 +14686,7 @@
         <v>13603.200000000003</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="125"/>
       <c r="B315" s="135"/>
       <c r="C315" s="133"/>
@@ -14703,7 +14703,7 @@
       <c r="N315" s="135"/>
       <c r="O315" s="138"/>
     </row>
-    <row r="316" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="125"/>
       <c r="B316" s="135"/>
       <c r="C316" s="135"/>
@@ -14720,7 +14720,7 @@
       <c r="N316" s="135"/>
       <c r="O316" s="138"/>
     </row>
-    <row r="317" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="125"/>
       <c r="B317" s="135"/>
       <c r="C317" s="135"/>
@@ -14741,28 +14741,28 @@
       <c r="N317" s="135"/>
       <c r="O317" s="138"/>
     </row>
-    <row r="318" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="125"/>
-      <c r="B318" s="248" t="s">
+      <c r="B318" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C318" s="248"/>
-      <c r="D318" s="248"/>
-      <c r="E318" s="248"/>
-      <c r="F318" s="248"/>
-      <c r="G318" s="248"/>
+      <c r="C318" s="247"/>
+      <c r="D318" s="247"/>
+      <c r="E318" s="247"/>
+      <c r="F318" s="247"/>
+      <c r="G318" s="247"/>
       <c r="H318" s="127"/>
       <c r="I318" s="127"/>
-      <c r="J318" s="248" t="s">
+      <c r="J318" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K318" s="248"/>
-      <c r="L318" s="248"/>
-      <c r="M318" s="248"/>
-      <c r="N318" s="248"/>
-      <c r="O318" s="248"/>
-    </row>
-    <row r="319" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K318" s="247"/>
+      <c r="L318" s="247"/>
+      <c r="M318" s="247"/>
+      <c r="N318" s="247"/>
+      <c r="O318" s="247"/>
+    </row>
+    <row r="319" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="125"/>
       <c r="B319" s="126"/>
       <c r="C319" s="128"/>
@@ -14779,28 +14779,28 @@
       <c r="N319" s="128"/>
       <c r="O319" s="128"/>
     </row>
-    <row r="320" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="125"/>
-      <c r="B320" s="247" t="s">
+      <c r="B320" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C320" s="247"/>
-      <c r="D320" s="247"/>
-      <c r="E320" s="247"/>
-      <c r="F320" s="247"/>
-      <c r="G320" s="247"/>
+      <c r="C320" s="248"/>
+      <c r="D320" s="248"/>
+      <c r="E320" s="248"/>
+      <c r="F320" s="248"/>
+      <c r="G320" s="248"/>
       <c r="H320" s="129"/>
       <c r="I320" s="130"/>
-      <c r="J320" s="247" t="s">
+      <c r="J320" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K320" s="247"/>
-      <c r="L320" s="247"/>
-      <c r="M320" s="247"/>
-      <c r="N320" s="247"/>
-      <c r="O320" s="247"/>
-    </row>
-    <row r="321" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K320" s="248"/>
+      <c r="L320" s="248"/>
+      <c r="M320" s="248"/>
+      <c r="N320" s="248"/>
+      <c r="O320" s="248"/>
+    </row>
+    <row r="321" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="125"/>
       <c r="B321" s="131">
         <f>+B292+1</f>
@@ -14822,7 +14822,7 @@
       <c r="N321" s="132"/>
       <c r="O321" s="132"/>
     </row>
-    <row r="322" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="125"/>
       <c r="B322" s="133" t="s">
         <v>93</v>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="O322" s="136"/>
     </row>
-    <row r="323" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="125"/>
       <c r="B323" s="133" t="s">
         <v>94</v>
@@ -14880,7 +14880,7 @@
       <c r="M323" s="135"/>
       <c r="O323" s="135"/>
     </row>
-    <row r="324" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="125"/>
       <c r="B324" s="133" t="s">
         <v>95</v>
@@ -14907,7 +14907,7 @@
       <c r="N324" s="135"/>
       <c r="O324" s="135"/>
     </row>
-    <row r="325" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="125"/>
       <c r="B325" s="133"/>
       <c r="C325" s="135"/>
@@ -14924,7 +14924,7 @@
       <c r="N325" s="135"/>
       <c r="O325" s="135"/>
     </row>
-    <row r="326" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="125"/>
       <c r="B326" s="133" t="s">
         <v>96</v>
@@ -14951,7 +14951,7 @@
         <v>14879.000000000002</v>
       </c>
     </row>
-    <row r="327" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="125"/>
       <c r="B327" s="133" t="s">
         <v>97</v>
@@ -14978,7 +14978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="125"/>
       <c r="B328" s="133" t="s">
         <v>98</v>
@@ -15004,7 +15004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="125"/>
       <c r="B329" s="133" t="s">
         <v>99</v>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="125"/>
       <c r="B330" s="135"/>
       <c r="C330" s="135"/>
@@ -15056,7 +15056,7 @@
         <v>14879.000000000002</v>
       </c>
     </row>
-    <row r="331" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="125"/>
       <c r="B331" s="135"/>
       <c r="C331" s="135"/>
@@ -15073,7 +15073,7 @@
       <c r="N331" s="135"/>
       <c r="O331" s="138"/>
     </row>
-    <row r="332" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="125"/>
       <c r="B332" s="135"/>
       <c r="C332" s="133" t="s">
@@ -15093,7 +15093,7 @@
       <c r="M332" s="135"/>
       <c r="O332" s="138"/>
     </row>
-    <row r="333" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="125"/>
       <c r="B333" s="135"/>
       <c r="C333" s="135"/>
@@ -15119,7 +15119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="125"/>
       <c r="B334" s="135"/>
       <c r="C334" s="135"/>
@@ -15145,7 +15145,7 @@
         <v>446.37000000000006</v>
       </c>
     </row>
-    <row r="335" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="125"/>
       <c r="B335" s="135"/>
       <c r="C335" s="135"/>
@@ -15171,7 +15171,7 @@
         <v>148.79000000000002</v>
       </c>
     </row>
-    <row r="336" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="125"/>
       <c r="B336" s="135"/>
       <c r="C336" s="135"/>
@@ -15194,7 +15194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="125"/>
       <c r="B337" s="135"/>
       <c r="C337" s="135"/>
@@ -15217,7 +15217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="125"/>
       <c r="B338" s="135"/>
       <c r="C338" s="135"/>
@@ -15240,7 +15240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="125"/>
       <c r="B339" s="135"/>
       <c r="C339" s="135"/>
@@ -15267,7 +15267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="125"/>
       <c r="B340" s="135"/>
       <c r="C340" s="135"/>
@@ -15291,7 +15291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="125"/>
       <c r="B341" s="135"/>
       <c r="C341" s="135"/>
@@ -15318,7 +15318,7 @@
         <v>595.16000000000008</v>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="125"/>
       <c r="B342" s="135"/>
       <c r="C342" s="135"/>
@@ -15335,7 +15335,7 @@
       <c r="N342" s="135"/>
       <c r="O342" s="138"/>
     </row>
-    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="125"/>
       <c r="B343" s="135"/>
       <c r="C343" s="133" t="s">
@@ -15362,7 +15362,7 @@
         <v>14283.840000000002</v>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="125"/>
       <c r="B344" s="135"/>
       <c r="C344" s="133"/>
@@ -15379,7 +15379,7 @@
       <c r="N344" s="135"/>
       <c r="O344" s="138"/>
     </row>
-    <row r="345" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="125"/>
       <c r="B345" s="135"/>
       <c r="C345" s="135"/>
@@ -15396,7 +15396,7 @@
       <c r="N345" s="135"/>
       <c r="O345" s="138"/>
     </row>
-    <row r="346" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="125"/>
       <c r="B346" s="135"/>
       <c r="C346" s="135"/>
@@ -15417,28 +15417,28 @@
       <c r="N346" s="135"/>
       <c r="O346" s="138"/>
     </row>
-    <row r="347" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="125"/>
-      <c r="B347" s="248" t="s">
+      <c r="B347" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C347" s="248"/>
-      <c r="D347" s="248"/>
-      <c r="E347" s="248"/>
-      <c r="F347" s="248"/>
-      <c r="G347" s="248"/>
+      <c r="C347" s="247"/>
+      <c r="D347" s="247"/>
+      <c r="E347" s="247"/>
+      <c r="F347" s="247"/>
+      <c r="G347" s="247"/>
       <c r="H347" s="127"/>
       <c r="I347" s="127"/>
-      <c r="J347" s="248" t="s">
+      <c r="J347" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K347" s="248"/>
-      <c r="L347" s="248"/>
-      <c r="M347" s="248"/>
-      <c r="N347" s="248"/>
-      <c r="O347" s="248"/>
-    </row>
-    <row r="348" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K347" s="247"/>
+      <c r="L347" s="247"/>
+      <c r="M347" s="247"/>
+      <c r="N347" s="247"/>
+      <c r="O347" s="247"/>
+    </row>
+    <row r="348" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="125"/>
       <c r="B348" s="126"/>
       <c r="C348" s="128"/>
@@ -15455,28 +15455,28 @@
       <c r="N348" s="128"/>
       <c r="O348" s="128"/>
     </row>
-    <row r="349" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="125"/>
-      <c r="B349" s="247" t="s">
+      <c r="B349" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C349" s="247"/>
-      <c r="D349" s="247"/>
-      <c r="E349" s="247"/>
-      <c r="F349" s="247"/>
-      <c r="G349" s="247"/>
+      <c r="C349" s="248"/>
+      <c r="D349" s="248"/>
+      <c r="E349" s="248"/>
+      <c r="F349" s="248"/>
+      <c r="G349" s="248"/>
       <c r="H349" s="129"/>
       <c r="I349" s="130"/>
-      <c r="J349" s="247" t="s">
+      <c r="J349" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K349" s="247"/>
-      <c r="L349" s="247"/>
-      <c r="M349" s="247"/>
-      <c r="N349" s="247"/>
-      <c r="O349" s="247"/>
-    </row>
-    <row r="350" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K349" s="248"/>
+      <c r="L349" s="248"/>
+      <c r="M349" s="248"/>
+      <c r="N349" s="248"/>
+      <c r="O349" s="248"/>
+    </row>
+    <row r="350" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="125"/>
       <c r="B350" s="131">
         <f>+B321+1</f>
@@ -15499,7 +15499,7 @@
       <c r="N350" s="132"/>
       <c r="O350" s="132"/>
     </row>
-    <row r="351" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="125"/>
       <c r="B351" s="133" t="s">
         <v>93</v>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="O351" s="136"/>
     </row>
-    <row r="352" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="125"/>
       <c r="B352" s="133" t="s">
         <v>94</v>
@@ -15557,7 +15557,7 @@
       <c r="M352" s="135"/>
       <c r="O352" s="135"/>
     </row>
-    <row r="353" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="125"/>
       <c r="B353" s="133" t="s">
         <v>95</v>
@@ -15584,7 +15584,7 @@
       <c r="N353" s="135"/>
       <c r="O353" s="135"/>
     </row>
-    <row r="354" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="125"/>
       <c r="B354" s="133"/>
       <c r="C354" s="135"/>
@@ -15601,7 +15601,7 @@
       <c r="N354" s="135"/>
       <c r="O354" s="135"/>
     </row>
-    <row r="355" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="125"/>
       <c r="B355" s="133" t="s">
         <v>96</v>
@@ -15628,7 +15628,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="356" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="125"/>
       <c r="B356" s="133" t="s">
         <v>97</v>
@@ -15655,7 +15655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="125"/>
       <c r="B357" s="133" t="s">
         <v>98</v>
@@ -15681,7 +15681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="125"/>
       <c r="B358" s="133" t="s">
         <v>99</v>
@@ -15707,7 +15707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="125"/>
       <c r="B359" s="135"/>
       <c r="C359" s="135"/>
@@ -15734,7 +15734,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="360" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="125"/>
       <c r="B360" s="135"/>
       <c r="C360" s="135"/>
@@ -15751,7 +15751,7 @@
       <c r="N360" s="135"/>
       <c r="O360" s="138"/>
     </row>
-    <row r="361" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="125"/>
       <c r="B361" s="135"/>
       <c r="C361" s="133" t="s">
@@ -15772,7 +15772,7 @@
       <c r="N361" s="135"/>
       <c r="O361" s="138"/>
     </row>
-    <row r="362" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="125"/>
       <c r="B362" s="135"/>
       <c r="C362" s="135"/>
@@ -15799,7 +15799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="125"/>
       <c r="B363" s="135"/>
       <c r="C363" s="135"/>
@@ -15826,7 +15826,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="125"/>
       <c r="B364" s="135"/>
       <c r="C364" s="135"/>
@@ -15853,7 +15853,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="125"/>
       <c r="B365" s="135"/>
       <c r="C365" s="135"/>
@@ -15877,7 +15877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="125"/>
       <c r="B366" s="135"/>
       <c r="C366" s="135"/>
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="125"/>
       <c r="B367" s="135"/>
       <c r="C367" s="135"/>
@@ -15925,7 +15925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="125"/>
       <c r="B368" s="135"/>
       <c r="C368" s="135"/>
@@ -15952,7 +15952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="125"/>
       <c r="B369" s="135"/>
       <c r="C369" s="135"/>
@@ -15978,7 +15978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="125"/>
       <c r="B370" s="135"/>
       <c r="C370" s="135"/>
@@ -16005,7 +16005,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="125"/>
       <c r="B371" s="135"/>
       <c r="C371" s="135"/>
@@ -16022,7 +16022,7 @@
       <c r="N371" s="135"/>
       <c r="O371" s="138"/>
     </row>
-    <row r="372" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="125"/>
       <c r="B372" s="135"/>
       <c r="C372" s="133" t="s">
@@ -16049,7 +16049,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="125"/>
       <c r="B373" s="135"/>
       <c r="C373" s="133"/>
@@ -16066,7 +16066,7 @@
       <c r="N373" s="135"/>
       <c r="O373" s="138"/>
     </row>
-    <row r="374" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="125"/>
       <c r="B374" s="135"/>
       <c r="C374" s="135"/>
@@ -16083,7 +16083,7 @@
       <c r="N374" s="135"/>
       <c r="O374" s="138"/>
     </row>
-    <row r="375" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="125"/>
       <c r="B375" s="135"/>
       <c r="C375" s="135"/>
@@ -16104,28 +16104,28 @@
       <c r="N375" s="135"/>
       <c r="O375" s="138"/>
     </row>
-    <row r="376" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="125"/>
-      <c r="B376" s="248" t="s">
+      <c r="B376" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C376" s="248"/>
-      <c r="D376" s="248"/>
-      <c r="E376" s="248"/>
-      <c r="F376" s="248"/>
-      <c r="G376" s="248"/>
+      <c r="C376" s="247"/>
+      <c r="D376" s="247"/>
+      <c r="E376" s="247"/>
+      <c r="F376" s="247"/>
+      <c r="G376" s="247"/>
       <c r="H376" s="127"/>
       <c r="I376" s="127"/>
-      <c r="J376" s="248" t="s">
+      <c r="J376" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K376" s="248"/>
-      <c r="L376" s="248"/>
-      <c r="M376" s="248"/>
-      <c r="N376" s="248"/>
-      <c r="O376" s="248"/>
-    </row>
-    <row r="377" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K376" s="247"/>
+      <c r="L376" s="247"/>
+      <c r="M376" s="247"/>
+      <c r="N376" s="247"/>
+      <c r="O376" s="247"/>
+    </row>
+    <row r="377" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="125"/>
       <c r="B377" s="126"/>
       <c r="C377" s="128"/>
@@ -16142,28 +16142,28 @@
       <c r="N377" s="128"/>
       <c r="O377" s="128"/>
     </row>
-    <row r="378" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="125"/>
-      <c r="B378" s="247" t="s">
+      <c r="B378" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C378" s="247"/>
-      <c r="D378" s="247"/>
-      <c r="E378" s="247"/>
-      <c r="F378" s="247"/>
-      <c r="G378" s="247"/>
+      <c r="C378" s="248"/>
+      <c r="D378" s="248"/>
+      <c r="E378" s="248"/>
+      <c r="F378" s="248"/>
+      <c r="G378" s="248"/>
       <c r="H378" s="129"/>
       <c r="I378" s="130"/>
-      <c r="J378" s="247" t="s">
+      <c r="J378" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K378" s="247"/>
-      <c r="L378" s="247"/>
-      <c r="M378" s="247"/>
-      <c r="N378" s="247"/>
-      <c r="O378" s="247"/>
-    </row>
-    <row r="379" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K378" s="248"/>
+      <c r="L378" s="248"/>
+      <c r="M378" s="248"/>
+      <c r="N378" s="248"/>
+      <c r="O378" s="248"/>
+    </row>
+    <row r="379" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="125"/>
       <c r="B379" s="131">
         <f>+B350+1</f>
@@ -16186,7 +16186,7 @@
       <c r="N379" s="132"/>
       <c r="O379" s="132"/>
     </row>
-    <row r="380" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="125"/>
       <c r="B380" s="133" t="s">
         <v>93</v>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="O380" s="136"/>
     </row>
-    <row r="381" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="125"/>
       <c r="B381" s="133" t="s">
         <v>94</v>
@@ -16244,7 +16244,7 @@
       <c r="M381" s="135"/>
       <c r="O381" s="135"/>
     </row>
-    <row r="382" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="125"/>
       <c r="B382" s="133" t="s">
         <v>95</v>
@@ -16268,7 +16268,7 @@
       <c r="N382" s="135"/>
       <c r="O382" s="135"/>
     </row>
-    <row r="383" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="125"/>
       <c r="B383" s="133"/>
       <c r="C383" s="135"/>
@@ -16285,7 +16285,7 @@
       <c r="N383" s="135"/>
       <c r="O383" s="135"/>
     </row>
-    <row r="384" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="125"/>
       <c r="B384" s="133" t="s">
         <v>96</v>
@@ -16312,7 +16312,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="385" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="125"/>
       <c r="B385" s="133" t="s">
         <v>97</v>
@@ -16339,7 +16339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="125"/>
       <c r="B386" s="133" t="s">
         <v>98</v>
@@ -16365,7 +16365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="125"/>
       <c r="B387" s="133" t="s">
         <v>99</v>
@@ -16391,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="125"/>
       <c r="B388" s="135"/>
       <c r="C388" s="135"/>
@@ -16418,7 +16418,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="389" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="125"/>
       <c r="B389" s="135"/>
       <c r="C389" s="135"/>
@@ -16435,7 +16435,7 @@
       <c r="N389" s="135"/>
       <c r="O389" s="138"/>
     </row>
-    <row r="390" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="125"/>
       <c r="B390" s="135"/>
       <c r="C390" s="133" t="s">
@@ -16455,7 +16455,7 @@
       <c r="N390" s="135"/>
       <c r="O390" s="138"/>
     </row>
-    <row r="391" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="125"/>
       <c r="B391" s="135"/>
       <c r="C391" s="135"/>
@@ -16481,7 +16481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="125"/>
       <c r="B392" s="135"/>
       <c r="C392" s="135"/>
@@ -16507,7 +16507,7 @@
         <v>490.50000000000011</v>
       </c>
     </row>
-    <row r="393" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="125"/>
       <c r="B393" s="135"/>
       <c r="C393" s="135"/>
@@ -16533,7 +16533,7 @@
         <v>163.50000000000003</v>
       </c>
     </row>
-    <row r="394" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="125"/>
       <c r="B394" s="135"/>
       <c r="C394" s="135"/>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="125"/>
       <c r="B395" s="135"/>
       <c r="C395" s="135"/>
@@ -16579,7 +16579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="125"/>
       <c r="B396" s="135"/>
       <c r="C396" s="135"/>
@@ -16602,7 +16602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="125"/>
       <c r="B397" s="135"/>
       <c r="C397" s="135"/>
@@ -16629,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="125"/>
       <c r="B398" s="135"/>
       <c r="C398" s="135"/>
@@ -16655,7 +16655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="125"/>
       <c r="B399" s="135"/>
       <c r="C399" s="135"/>
@@ -16682,7 +16682,7 @@
         <v>654.00000000000011</v>
       </c>
     </row>
-    <row r="400" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="125"/>
       <c r="B400" s="135"/>
       <c r="C400" s="135"/>
@@ -16699,7 +16699,7 @@
       <c r="N400" s="135"/>
       <c r="O400" s="138"/>
     </row>
-    <row r="401" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="125"/>
       <c r="B401" s="135"/>
       <c r="C401" s="133" t="s">
@@ -16726,7 +16726,7 @@
         <v>15696.000000000004</v>
       </c>
     </row>
-    <row r="402" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="125"/>
       <c r="B402" s="135"/>
       <c r="C402" s="133"/>
@@ -16743,7 +16743,7 @@
       <c r="N402" s="135"/>
       <c r="O402" s="138"/>
     </row>
-    <row r="403" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="125"/>
       <c r="B403" s="135"/>
       <c r="C403" s="135"/>
@@ -16760,7 +16760,7 @@
       <c r="N403" s="135"/>
       <c r="O403" s="138"/>
     </row>
-    <row r="404" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="125"/>
       <c r="B404" s="135"/>
       <c r="C404" s="135"/>
@@ -16781,28 +16781,28 @@
       <c r="N404" s="135"/>
       <c r="O404" s="138"/>
     </row>
-    <row r="405" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="125"/>
-      <c r="B405" s="248" t="s">
+      <c r="B405" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C405" s="248"/>
-      <c r="D405" s="248"/>
-      <c r="E405" s="248"/>
-      <c r="F405" s="248"/>
-      <c r="G405" s="248"/>
+      <c r="C405" s="247"/>
+      <c r="D405" s="247"/>
+      <c r="E405" s="247"/>
+      <c r="F405" s="247"/>
+      <c r="G405" s="247"/>
       <c r="H405" s="127"/>
       <c r="I405" s="127"/>
-      <c r="J405" s="248" t="s">
+      <c r="J405" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K405" s="248"/>
-      <c r="L405" s="248"/>
-      <c r="M405" s="248"/>
-      <c r="N405" s="248"/>
-      <c r="O405" s="248"/>
-    </row>
-    <row r="406" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K405" s="247"/>
+      <c r="L405" s="247"/>
+      <c r="M405" s="247"/>
+      <c r="N405" s="247"/>
+      <c r="O405" s="247"/>
+    </row>
+    <row r="406" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="125"/>
       <c r="B406" s="126"/>
       <c r="C406" s="128"/>
@@ -16819,28 +16819,28 @@
       <c r="N406" s="128"/>
       <c r="O406" s="128"/>
     </row>
-    <row r="407" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="125"/>
-      <c r="B407" s="247" t="s">
+      <c r="B407" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C407" s="247"/>
-      <c r="D407" s="247"/>
-      <c r="E407" s="247"/>
-      <c r="F407" s="247"/>
-      <c r="G407" s="247"/>
+      <c r="C407" s="248"/>
+      <c r="D407" s="248"/>
+      <c r="E407" s="248"/>
+      <c r="F407" s="248"/>
+      <c r="G407" s="248"/>
       <c r="H407" s="129"/>
       <c r="I407" s="130"/>
-      <c r="J407" s="247" t="s">
+      <c r="J407" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K407" s="247"/>
-      <c r="L407" s="247"/>
-      <c r="M407" s="247"/>
-      <c r="N407" s="247"/>
-      <c r="O407" s="247"/>
-    </row>
-    <row r="408" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K407" s="248"/>
+      <c r="L407" s="248"/>
+      <c r="M407" s="248"/>
+      <c r="N407" s="248"/>
+      <c r="O407" s="248"/>
+    </row>
+    <row r="408" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="125"/>
       <c r="B408" s="131">
         <f>+B379+1</f>
@@ -16863,7 +16863,7 @@
       <c r="N408" s="132"/>
       <c r="O408" s="132"/>
     </row>
-    <row r="409" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="125"/>
       <c r="B409" s="133" t="s">
         <v>93</v>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="O409" s="136"/>
     </row>
-    <row r="410" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="125"/>
       <c r="B410" s="133" t="s">
         <v>94</v>
@@ -16921,7 +16921,7 @@
       <c r="M410" s="135"/>
       <c r="O410" s="135"/>
     </row>
-    <row r="411" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="125"/>
       <c r="B411" s="133" t="s">
         <v>95</v>
@@ -16948,7 +16948,7 @@
       <c r="N411" s="135"/>
       <c r="O411" s="135"/>
     </row>
-    <row r="412" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="125"/>
       <c r="B412" s="133"/>
       <c r="C412" s="135"/>
@@ -16965,7 +16965,7 @@
       <c r="N412" s="135"/>
       <c r="O412" s="135"/>
     </row>
-    <row r="413" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="125"/>
       <c r="B413" s="133" t="s">
         <v>96</v>
@@ -16992,7 +16992,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="414" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="125"/>
       <c r="B414" s="133" t="s">
         <v>97</v>
@@ -17019,7 +17019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="125"/>
       <c r="B415" s="133" t="s">
         <v>98</v>
@@ -17045,7 +17045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="125"/>
       <c r="B416" s="133" t="s">
         <v>99</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="125"/>
       <c r="B417" s="135"/>
       <c r="C417" s="135"/>
@@ -17099,7 +17099,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="418" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="125"/>
       <c r="B418" s="135"/>
       <c r="C418" s="135"/>
@@ -17116,7 +17116,7 @@
       <c r="N418" s="135"/>
       <c r="O418" s="138"/>
     </row>
-    <row r="419" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="125"/>
       <c r="B419" s="135"/>
       <c r="C419" s="133" t="s">
@@ -17136,7 +17136,7 @@
       <c r="M419" s="135"/>
       <c r="O419" s="138"/>
     </row>
-    <row r="420" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="125"/>
       <c r="B420" s="135"/>
       <c r="C420" s="135"/>
@@ -17162,7 +17162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="125"/>
       <c r="B421" s="135"/>
       <c r="C421" s="135"/>
@@ -17188,7 +17188,7 @@
         <v>490.50000000000011</v>
       </c>
     </row>
-    <row r="422" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="125"/>
       <c r="B422" s="135"/>
       <c r="C422" s="135"/>
@@ -17214,7 +17214,7 @@
         <v>163.50000000000003</v>
       </c>
     </row>
-    <row r="423" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="125"/>
       <c r="B423" s="135"/>
       <c r="C423" s="135"/>
@@ -17237,7 +17237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="125"/>
       <c r="B424" s="135"/>
       <c r="C424" s="135"/>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="125"/>
       <c r="B425" s="135"/>
       <c r="C425" s="135"/>
@@ -17283,7 +17283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="125"/>
       <c r="B426" s="135"/>
       <c r="C426" s="135"/>
@@ -17310,7 +17310,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="125"/>
       <c r="B427" s="135"/>
       <c r="C427" s="135"/>
@@ -17336,7 +17336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="125"/>
       <c r="B428" s="135"/>
       <c r="C428" s="135"/>
@@ -17363,7 +17363,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="429" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="125"/>
       <c r="B429" s="135"/>
       <c r="C429" s="135"/>
@@ -17380,7 +17380,7 @@
       <c r="N429" s="135"/>
       <c r="O429" s="138"/>
     </row>
-    <row r="430" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="125"/>
       <c r="B430" s="135"/>
       <c r="C430" s="133" t="s">
@@ -17407,7 +17407,7 @@
         <v>14196.000000000004</v>
       </c>
     </row>
-    <row r="431" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="125"/>
       <c r="B431" s="135"/>
       <c r="C431" s="133"/>
@@ -17424,7 +17424,7 @@
       <c r="N431" s="135"/>
       <c r="O431" s="138"/>
     </row>
-    <row r="432" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="125"/>
       <c r="B432" s="135"/>
       <c r="C432" s="135"/>
@@ -17441,7 +17441,7 @@
       <c r="N432" s="135"/>
       <c r="O432" s="138"/>
     </row>
-    <row r="433" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="125"/>
       <c r="B433" s="135"/>
       <c r="C433" s="135"/>
@@ -17462,28 +17462,28 @@
       <c r="N433" s="135"/>
       <c r="O433" s="138"/>
     </row>
-    <row r="434" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="125"/>
-      <c r="B434" s="248" t="s">
+      <c r="B434" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C434" s="248"/>
-      <c r="D434" s="248"/>
-      <c r="E434" s="248"/>
-      <c r="F434" s="248"/>
-      <c r="G434" s="248"/>
+      <c r="C434" s="247"/>
+      <c r="D434" s="247"/>
+      <c r="E434" s="247"/>
+      <c r="F434" s="247"/>
+      <c r="G434" s="247"/>
       <c r="H434" s="127"/>
       <c r="I434" s="127"/>
-      <c r="J434" s="248" t="s">
+      <c r="J434" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K434" s="248"/>
-      <c r="L434" s="248"/>
-      <c r="M434" s="248"/>
-      <c r="N434" s="248"/>
-      <c r="O434" s="248"/>
-    </row>
-    <row r="435" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K434" s="247"/>
+      <c r="L434" s="247"/>
+      <c r="M434" s="247"/>
+      <c r="N434" s="247"/>
+      <c r="O434" s="247"/>
+    </row>
+    <row r="435" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="125"/>
       <c r="B435" s="126"/>
       <c r="C435" s="128"/>
@@ -17500,28 +17500,28 @@
       <c r="N435" s="128"/>
       <c r="O435" s="128"/>
     </row>
-    <row r="436" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="125"/>
-      <c r="B436" s="247" t="s">
+      <c r="B436" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C436" s="247"/>
-      <c r="D436" s="247"/>
-      <c r="E436" s="247"/>
-      <c r="F436" s="247"/>
-      <c r="G436" s="247"/>
+      <c r="C436" s="248"/>
+      <c r="D436" s="248"/>
+      <c r="E436" s="248"/>
+      <c r="F436" s="248"/>
+      <c r="G436" s="248"/>
       <c r="H436" s="129"/>
       <c r="I436" s="130"/>
-      <c r="J436" s="247" t="s">
+      <c r="J436" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K436" s="247"/>
-      <c r="L436" s="247"/>
-      <c r="M436" s="247"/>
-      <c r="N436" s="247"/>
-      <c r="O436" s="247"/>
-    </row>
-    <row r="437" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K436" s="248"/>
+      <c r="L436" s="248"/>
+      <c r="M436" s="248"/>
+      <c r="N436" s="248"/>
+      <c r="O436" s="248"/>
+    </row>
+    <row r="437" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="125"/>
       <c r="B437" s="131">
         <f>+B408+1</f>
@@ -17543,7 +17543,7 @@
       <c r="N437" s="132"/>
       <c r="O437" s="132"/>
     </row>
-    <row r="438" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="125"/>
       <c r="B438" s="133" t="s">
         <v>93</v>
@@ -17575,7 +17575,7 @@
       </c>
       <c r="O438" s="136"/>
     </row>
-    <row r="439" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="125"/>
       <c r="B439" s="133" t="s">
         <v>94</v>
@@ -17601,7 +17601,7 @@
       <c r="M439" s="135"/>
       <c r="O439" s="135"/>
     </row>
-    <row r="440" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="125"/>
       <c r="B440" s="133" t="s">
         <v>95</v>
@@ -17628,7 +17628,7 @@
       <c r="N440" s="135"/>
       <c r="O440" s="135"/>
     </row>
-    <row r="441" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="125"/>
       <c r="B441" s="133"/>
       <c r="C441" s="135"/>
@@ -17645,7 +17645,7 @@
       <c r="N441" s="135"/>
       <c r="O441" s="135"/>
     </row>
-    <row r="442" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="125"/>
       <c r="B442" s="133" t="s">
         <v>96</v>
@@ -17672,7 +17672,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="125"/>
       <c r="B443" s="133" t="s">
         <v>97</v>
@@ -17699,7 +17699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="125"/>
       <c r="B444" s="133" t="s">
         <v>98</v>
@@ -17725,7 +17725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="125"/>
       <c r="B445" s="133" t="s">
         <v>99</v>
@@ -17750,7 +17750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="125"/>
       <c r="B446" s="135"/>
       <c r="C446" s="135"/>
@@ -17777,7 +17777,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="447" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="125"/>
       <c r="B447" s="135"/>
       <c r="C447" s="135"/>
@@ -17794,7 +17794,7 @@
       <c r="N447" s="135"/>
       <c r="O447" s="138"/>
     </row>
-    <row r="448" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="125"/>
       <c r="B448" s="135"/>
       <c r="C448" s="133" t="s">
@@ -17814,7 +17814,7 @@
       <c r="N448" s="135"/>
       <c r="O448" s="138"/>
     </row>
-    <row r="449" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="125"/>
       <c r="B449" s="135"/>
       <c r="C449" s="135"/>
@@ -17840,7 +17840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="125"/>
       <c r="B450" s="135"/>
       <c r="C450" s="135"/>
@@ -17866,7 +17866,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="451" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="125"/>
       <c r="B451" s="135"/>
       <c r="C451" s="135"/>
@@ -17892,7 +17892,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="452" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="125"/>
       <c r="B452" s="135"/>
       <c r="C452" s="135"/>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="125"/>
       <c r="B453" s="135"/>
       <c r="C453" s="135"/>
@@ -17938,7 +17938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="125"/>
       <c r="B454" s="135"/>
       <c r="C454" s="135"/>
@@ -17961,7 +17961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="125"/>
       <c r="B455" s="135"/>
       <c r="C455" s="135"/>
@@ -17988,7 +17988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="125"/>
       <c r="B456" s="135"/>
       <c r="C456" s="135"/>
@@ -18015,7 +18015,7 @@
         <v>457.79999999999995</v>
       </c>
     </row>
-    <row r="457" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="125"/>
       <c r="B457" s="135"/>
       <c r="C457" s="135"/>
@@ -18032,7 +18032,7 @@
       <c r="N457" s="135"/>
       <c r="O457" s="138"/>
     </row>
-    <row r="458" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="125"/>
       <c r="B458" s="135"/>
       <c r="C458" s="133" t="s">
@@ -18059,7 +18059,7 @@
         <v>10987.2</v>
       </c>
     </row>
-    <row r="459" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="125"/>
       <c r="B459" s="135"/>
       <c r="C459" s="133"/>
@@ -18076,7 +18076,7 @@
       <c r="N459" s="135"/>
       <c r="O459" s="138"/>
     </row>
-    <row r="460" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="125"/>
       <c r="B460" s="135"/>
       <c r="C460" s="135"/>
@@ -18093,7 +18093,7 @@
       <c r="N460" s="135"/>
       <c r="O460" s="138"/>
     </row>
-    <row r="461" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="125"/>
       <c r="B461" s="135"/>
       <c r="C461" s="135"/>
@@ -18114,28 +18114,28 @@
       <c r="N461" s="135"/>
       <c r="O461" s="138"/>
     </row>
-    <row r="462" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="125"/>
-      <c r="B462" s="248" t="s">
+      <c r="B462" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C462" s="248"/>
-      <c r="D462" s="248"/>
-      <c r="E462" s="248"/>
-      <c r="F462" s="248"/>
-      <c r="G462" s="248"/>
+      <c r="C462" s="247"/>
+      <c r="D462" s="247"/>
+      <c r="E462" s="247"/>
+      <c r="F462" s="247"/>
+      <c r="G462" s="247"/>
       <c r="H462" s="127"/>
       <c r="I462" s="127"/>
-      <c r="J462" s="248" t="s">
+      <c r="J462" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K462" s="248"/>
-      <c r="L462" s="248"/>
-      <c r="M462" s="248"/>
-      <c r="N462" s="248"/>
-      <c r="O462" s="248"/>
-    </row>
-    <row r="463" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K462" s="247"/>
+      <c r="L462" s="247"/>
+      <c r="M462" s="247"/>
+      <c r="N462" s="247"/>
+      <c r="O462" s="247"/>
+    </row>
+    <row r="463" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="125"/>
       <c r="B463" s="126"/>
       <c r="C463" s="128"/>
@@ -18152,28 +18152,28 @@
       <c r="N463" s="128"/>
       <c r="O463" s="128"/>
     </row>
-    <row r="464" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="125"/>
-      <c r="B464" s="247" t="s">
+      <c r="B464" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C464" s="247"/>
-      <c r="D464" s="247"/>
-      <c r="E464" s="247"/>
-      <c r="F464" s="247"/>
-      <c r="G464" s="247"/>
+      <c r="C464" s="248"/>
+      <c r="D464" s="248"/>
+      <c r="E464" s="248"/>
+      <c r="F464" s="248"/>
+      <c r="G464" s="248"/>
       <c r="H464" s="129"/>
       <c r="I464" s="130"/>
-      <c r="J464" s="247" t="s">
+      <c r="J464" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K464" s="247"/>
-      <c r="L464" s="247"/>
-      <c r="M464" s="247"/>
-      <c r="N464" s="247"/>
-      <c r="O464" s="247"/>
-    </row>
-    <row r="465" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K464" s="248"/>
+      <c r="L464" s="248"/>
+      <c r="M464" s="248"/>
+      <c r="N464" s="248"/>
+      <c r="O464" s="248"/>
+    </row>
+    <row r="465" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="125"/>
       <c r="B465" s="131">
         <f>+B437+1</f>
@@ -18195,7 +18195,7 @@
       <c r="N465" s="132"/>
       <c r="O465" s="132"/>
     </row>
-    <row r="466" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="125"/>
       <c r="B466" s="133" t="s">
         <v>93</v>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="O466" s="136"/>
     </row>
-    <row r="467" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="125"/>
       <c r="B467" s="133" t="s">
         <v>94</v>
@@ -18253,7 +18253,7 @@
       <c r="M467" s="135"/>
       <c r="O467" s="135"/>
     </row>
-    <row r="468" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="125"/>
       <c r="B468" s="133" t="s">
         <v>95</v>
@@ -18280,7 +18280,7 @@
       <c r="N468" s="135"/>
       <c r="O468" s="135"/>
     </row>
-    <row r="469" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="125"/>
       <c r="B469" s="133"/>
       <c r="C469" s="135"/>
@@ -18297,7 +18297,7 @@
       <c r="N469" s="135"/>
       <c r="O469" s="135"/>
     </row>
-    <row r="470" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="125"/>
       <c r="B470" s="133" t="s">
         <v>96</v>
@@ -18324,7 +18324,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="125"/>
       <c r="B471" s="133" t="s">
         <v>97</v>
@@ -18351,7 +18351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="125"/>
       <c r="B472" s="133" t="s">
         <v>98</v>
@@ -18377,7 +18377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="125"/>
       <c r="B473" s="133" t="s">
         <v>99</v>
@@ -18402,7 +18402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="125"/>
       <c r="B474" s="135"/>
       <c r="C474" s="135"/>
@@ -18429,7 +18429,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="475" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="125"/>
       <c r="B475" s="135"/>
       <c r="C475" s="135"/>
@@ -18446,7 +18446,7 @@
       <c r="N475" s="135"/>
       <c r="O475" s="138"/>
     </row>
-    <row r="476" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="125"/>
       <c r="B476" s="135"/>
       <c r="C476" s="133" t="s">
@@ -18466,7 +18466,7 @@
       <c r="M476" s="135"/>
       <c r="O476" s="138"/>
     </row>
-    <row r="477" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="125"/>
       <c r="B477" s="135"/>
       <c r="C477" s="135"/>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="125"/>
       <c r="B478" s="135"/>
       <c r="C478" s="135"/>
@@ -18518,7 +18518,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="479" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="125"/>
       <c r="B479" s="135"/>
       <c r="C479" s="135"/>
@@ -18544,7 +18544,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="480" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="125"/>
       <c r="B480" s="135"/>
       <c r="C480" s="135"/>
@@ -18567,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="125"/>
       <c r="B481" s="135"/>
       <c r="C481" s="135"/>
@@ -18590,7 +18590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="125"/>
       <c r="B482" s="135"/>
       <c r="C482" s="135"/>
@@ -18613,7 +18613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="125"/>
       <c r="B483" s="135"/>
       <c r="C483" s="135"/>
@@ -18640,7 +18640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="125"/>
       <c r="B484" s="135"/>
       <c r="C484" s="135"/>
@@ -18664,7 +18664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="125"/>
       <c r="B485" s="135"/>
       <c r="C485" s="135"/>
@@ -18691,7 +18691,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="486" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="125"/>
       <c r="B486" s="135"/>
       <c r="C486" s="135"/>
@@ -18708,7 +18708,7 @@
       <c r="N486" s="135"/>
       <c r="O486" s="138"/>
     </row>
-    <row r="487" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="125"/>
       <c r="B487" s="135"/>
       <c r="C487" s="133" t="s">
@@ -18735,7 +18735,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="125"/>
       <c r="B488" s="135"/>
       <c r="C488" s="133"/>
@@ -18752,7 +18752,7 @@
       <c r="N488" s="135"/>
       <c r="O488" s="138"/>
     </row>
-    <row r="489" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="125"/>
       <c r="B489" s="135"/>
       <c r="C489" s="135"/>
@@ -18769,7 +18769,7 @@
       <c r="N489" s="135"/>
       <c r="O489" s="138"/>
     </row>
-    <row r="490" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="125"/>
       <c r="B490" s="135"/>
       <c r="C490" s="135"/>
@@ -18790,28 +18790,28 @@
       <c r="N490" s="135"/>
       <c r="O490" s="138"/>
     </row>
-    <row r="491" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="125"/>
-      <c r="B491" s="248" t="s">
+      <c r="B491" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C491" s="248"/>
-      <c r="D491" s="248"/>
-      <c r="E491" s="248"/>
-      <c r="F491" s="248"/>
-      <c r="G491" s="248"/>
+      <c r="C491" s="247"/>
+      <c r="D491" s="247"/>
+      <c r="E491" s="247"/>
+      <c r="F491" s="247"/>
+      <c r="G491" s="247"/>
       <c r="H491" s="127"/>
       <c r="I491" s="127"/>
-      <c r="J491" s="248" t="s">
+      <c r="J491" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K491" s="248"/>
-      <c r="L491" s="248"/>
-      <c r="M491" s="248"/>
-      <c r="N491" s="248"/>
-      <c r="O491" s="248"/>
-    </row>
-    <row r="492" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K491" s="247"/>
+      <c r="L491" s="247"/>
+      <c r="M491" s="247"/>
+      <c r="N491" s="247"/>
+      <c r="O491" s="247"/>
+    </row>
+    <row r="492" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="125"/>
       <c r="B492" s="126"/>
       <c r="C492" s="128"/>
@@ -18828,28 +18828,28 @@
       <c r="N492" s="128"/>
       <c r="O492" s="128"/>
     </row>
-    <row r="493" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="125"/>
-      <c r="B493" s="247" t="s">
+      <c r="B493" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C493" s="247"/>
-      <c r="D493" s="247"/>
-      <c r="E493" s="247"/>
-      <c r="F493" s="247"/>
-      <c r="G493" s="247"/>
+      <c r="C493" s="248"/>
+      <c r="D493" s="248"/>
+      <c r="E493" s="248"/>
+      <c r="F493" s="248"/>
+      <c r="G493" s="248"/>
       <c r="H493" s="129"/>
       <c r="I493" s="130"/>
-      <c r="J493" s="247" t="s">
+      <c r="J493" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K493" s="247"/>
-      <c r="L493" s="247"/>
-      <c r="M493" s="247"/>
-      <c r="N493" s="247"/>
-      <c r="O493" s="247"/>
-    </row>
-    <row r="494" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K493" s="248"/>
+      <c r="L493" s="248"/>
+      <c r="M493" s="248"/>
+      <c r="N493" s="248"/>
+      <c r="O493" s="248"/>
+    </row>
+    <row r="494" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="125"/>
       <c r="B494" s="131">
         <f>+B465+1</f>
@@ -18872,7 +18872,7 @@
       <c r="N494" s="132"/>
       <c r="O494" s="132"/>
     </row>
-    <row r="495" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="125"/>
       <c r="B495" s="133" t="s">
         <v>93</v>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="O495" s="136"/>
     </row>
-    <row r="496" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="125"/>
       <c r="B496" s="133" t="s">
         <v>94</v>
@@ -18930,7 +18930,7 @@
       <c r="M496" s="135"/>
       <c r="O496" s="135"/>
     </row>
-    <row r="497" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="125"/>
       <c r="B497" s="133" t="s">
         <v>95</v>
@@ -18957,7 +18957,7 @@
       <c r="N497" s="135"/>
       <c r="O497" s="135"/>
     </row>
-    <row r="498" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="125"/>
       <c r="B498" s="133"/>
       <c r="C498" s="135"/>
@@ -18974,7 +18974,7 @@
       <c r="N498" s="135"/>
       <c r="O498" s="135"/>
     </row>
-    <row r="499" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="125"/>
       <c r="B499" s="133" t="s">
         <v>96</v>
@@ -19001,7 +19001,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="500" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="125"/>
       <c r="B500" s="133" t="s">
         <v>97</v>
@@ -19028,7 +19028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="125"/>
       <c r="B501" s="133" t="s">
         <v>98</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="125"/>
       <c r="B502" s="133" t="s">
         <v>99</v>
@@ -19080,7 +19080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="125"/>
       <c r="B503" s="135"/>
       <c r="C503" s="135"/>
@@ -19107,7 +19107,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="504" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="125"/>
       <c r="B504" s="135"/>
       <c r="C504" s="135"/>
@@ -19124,7 +19124,7 @@
       <c r="N504" s="135"/>
       <c r="O504" s="138"/>
     </row>
-    <row r="505" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="125"/>
       <c r="B505" s="135"/>
       <c r="C505" s="133" t="s">
@@ -19144,7 +19144,7 @@
       <c r="M505" s="135"/>
       <c r="O505" s="138"/>
     </row>
-    <row r="506" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="125"/>
       <c r="B506" s="135"/>
       <c r="C506" s="135"/>
@@ -19170,7 +19170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="125"/>
       <c r="B507" s="135"/>
       <c r="C507" s="135"/>
@@ -19196,7 +19196,7 @@
         <v>426.75000000000006</v>
       </c>
     </row>
-    <row r="508" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="125"/>
       <c r="B508" s="135"/>
       <c r="C508" s="135"/>
@@ -19222,7 +19222,7 @@
         <v>142.25000000000003</v>
       </c>
     </row>
-    <row r="509" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="125"/>
       <c r="B509" s="135"/>
       <c r="C509" s="135"/>
@@ -19245,7 +19245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="125"/>
       <c r="B510" s="135"/>
       <c r="C510" s="135"/>
@@ -19268,7 +19268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="125"/>
       <c r="B511" s="135"/>
       <c r="C511" s="135"/>
@@ -19291,7 +19291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="125"/>
       <c r="B512" s="135"/>
       <c r="C512" s="135"/>
@@ -19318,7 +19318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="125"/>
       <c r="B513" s="135"/>
       <c r="C513" s="135"/>
@@ -19342,7 +19342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="125"/>
       <c r="B514" s="135"/>
       <c r="C514" s="135"/>
@@ -19369,7 +19369,7 @@
         <v>569.00000000000011</v>
       </c>
     </row>
-    <row r="515" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="125"/>
       <c r="B515" s="135"/>
       <c r="C515" s="135"/>
@@ -19386,7 +19386,7 @@
       <c r="N515" s="135"/>
       <c r="O515" s="138"/>
     </row>
-    <row r="516" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="125"/>
       <c r="B516" s="135"/>
       <c r="C516" s="133" t="s">
@@ -19413,7 +19413,7 @@
         <v>13656.000000000002</v>
       </c>
     </row>
-    <row r="517" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="125"/>
       <c r="B517" s="135"/>
       <c r="C517" s="133"/>
@@ -19430,7 +19430,7 @@
       <c r="N517" s="135"/>
       <c r="O517" s="138"/>
     </row>
-    <row r="518" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="125"/>
       <c r="B518" s="135"/>
       <c r="C518" s="135"/>
@@ -19447,7 +19447,7 @@
       <c r="N518" s="135"/>
       <c r="O518" s="138"/>
     </row>
-    <row r="519" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="125"/>
       <c r="B519" s="135"/>
       <c r="C519" s="135"/>
@@ -19468,28 +19468,28 @@
       <c r="N519" s="135"/>
       <c r="O519" s="138"/>
     </row>
-    <row r="520" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="125"/>
-      <c r="B520" s="248" t="s">
+      <c r="B520" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C520" s="248"/>
-      <c r="D520" s="248"/>
-      <c r="E520" s="248"/>
-      <c r="F520" s="248"/>
-      <c r="G520" s="248"/>
+      <c r="C520" s="247"/>
+      <c r="D520" s="247"/>
+      <c r="E520" s="247"/>
+      <c r="F520" s="247"/>
+      <c r="G520" s="247"/>
       <c r="H520" s="127"/>
       <c r="I520" s="127"/>
-      <c r="J520" s="248" t="s">
+      <c r="J520" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K520" s="248"/>
-      <c r="L520" s="248"/>
-      <c r="M520" s="248"/>
-      <c r="N520" s="248"/>
-      <c r="O520" s="248"/>
-    </row>
-    <row r="521" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K520" s="247"/>
+      <c r="L520" s="247"/>
+      <c r="M520" s="247"/>
+      <c r="N520" s="247"/>
+      <c r="O520" s="247"/>
+    </row>
+    <row r="521" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="125"/>
       <c r="B521" s="126"/>
       <c r="C521" s="128"/>
@@ -19506,28 +19506,28 @@
       <c r="N521" s="128"/>
       <c r="O521" s="128"/>
     </row>
-    <row r="522" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="125"/>
-      <c r="B522" s="247" t="s">
+      <c r="B522" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C522" s="247"/>
-      <c r="D522" s="247"/>
-      <c r="E522" s="247"/>
-      <c r="F522" s="247"/>
-      <c r="G522" s="247"/>
+      <c r="C522" s="248"/>
+      <c r="D522" s="248"/>
+      <c r="E522" s="248"/>
+      <c r="F522" s="248"/>
+      <c r="G522" s="248"/>
       <c r="H522" s="129"/>
       <c r="I522" s="130"/>
-      <c r="J522" s="247" t="s">
+      <c r="J522" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K522" s="247"/>
-      <c r="L522" s="247"/>
-      <c r="M522" s="247"/>
-      <c r="N522" s="247"/>
-      <c r="O522" s="247"/>
-    </row>
-    <row r="523" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K522" s="248"/>
+      <c r="L522" s="248"/>
+      <c r="M522" s="248"/>
+      <c r="N522" s="248"/>
+      <c r="O522" s="248"/>
+    </row>
+    <row r="523" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="125"/>
       <c r="B523" s="131">
         <f>+'Folha de salarios'!A28</f>
@@ -19549,7 +19549,7 @@
       <c r="N523" s="132"/>
       <c r="O523" s="132"/>
     </row>
-    <row r="524" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="125"/>
       <c r="B524" s="133" t="s">
         <v>93</v>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="O524" s="136"/>
     </row>
-    <row r="525" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="125"/>
       <c r="B525" s="133" t="s">
         <v>94</v>
@@ -19607,7 +19607,7 @@
       <c r="M525" s="135"/>
       <c r="O525" s="135"/>
     </row>
-    <row r="526" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="125"/>
       <c r="B526" s="133" t="s">
         <v>95</v>
@@ -19634,7 +19634,7 @@
       <c r="N526" s="135"/>
       <c r="O526" s="135"/>
     </row>
-    <row r="527" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="125"/>
       <c r="B527" s="133"/>
       <c r="C527" s="135"/>
@@ -19651,7 +19651,7 @@
       <c r="N527" s="135"/>
       <c r="O527" s="135"/>
     </row>
-    <row r="528" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="125"/>
       <c r="B528" s="133" t="s">
         <v>96</v>
@@ -19678,7 +19678,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="529" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="125"/>
       <c r="B529" s="133" t="s">
         <v>97</v>
@@ -19705,7 +19705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="125"/>
       <c r="B530" s="133" t="s">
         <v>98</v>
@@ -19731,7 +19731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="125"/>
       <c r="B531" s="133" t="s">
         <v>99</v>
@@ -19756,7 +19756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="125"/>
       <c r="B532" s="135"/>
       <c r="C532" s="135"/>
@@ -19783,7 +19783,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="533" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="125"/>
       <c r="B533" s="135"/>
       <c r="C533" s="135"/>
@@ -19800,7 +19800,7 @@
       <c r="N533" s="135"/>
       <c r="O533" s="138"/>
     </row>
-    <row r="534" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="125"/>
       <c r="B534" s="135"/>
       <c r="C534" s="133" t="s">
@@ -19820,7 +19820,7 @@
       <c r="N534" s="135"/>
       <c r="O534" s="138"/>
     </row>
-    <row r="535" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="125"/>
       <c r="B535" s="135"/>
       <c r="C535" s="135"/>
@@ -19846,7 +19846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="125"/>
       <c r="B536" s="135"/>
       <c r="C536" s="135"/>
@@ -19872,7 +19872,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="537" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="125"/>
       <c r="B537" s="135"/>
       <c r="C537" s="135"/>
@@ -19898,7 +19898,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="538" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="125"/>
       <c r="B538" s="135"/>
       <c r="C538" s="135"/>
@@ -19921,7 +19921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="125"/>
       <c r="B539" s="135"/>
       <c r="C539" s="135"/>
@@ -19944,7 +19944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="125"/>
       <c r="B540" s="135"/>
       <c r="C540" s="135"/>
@@ -19967,7 +19967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="125"/>
       <c r="B541" s="135"/>
       <c r="C541" s="135"/>
@@ -19994,7 +19994,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="542" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="125"/>
       <c r="B542" s="135"/>
       <c r="C542" s="135"/>
@@ -20020,7 +20020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="125"/>
       <c r="B543" s="135"/>
       <c r="C543" s="135"/>
@@ -20047,7 +20047,7 @@
         <v>5457.8</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="125"/>
       <c r="B544" s="135"/>
       <c r="C544" s="135"/>
@@ -20064,7 +20064,7 @@
       <c r="N544" s="135"/>
       <c r="O544" s="138"/>
     </row>
-    <row r="545" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="125"/>
       <c r="B545" s="135"/>
       <c r="C545" s="133" t="s">
@@ -20091,7 +20091,7 @@
         <v>5987.2</v>
       </c>
     </row>
-    <row r="546" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="125"/>
       <c r="B546" s="135"/>
       <c r="C546" s="133"/>
@@ -20108,7 +20108,7 @@
       <c r="N546" s="135"/>
       <c r="O546" s="138"/>
     </row>
-    <row r="547" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="125"/>
       <c r="B547" s="135"/>
       <c r="C547" s="135"/>
@@ -20125,7 +20125,7 @@
       <c r="N547" s="135"/>
       <c r="O547" s="138"/>
     </row>
-    <row r="548" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="125"/>
       <c r="B548" s="135"/>
       <c r="C548" s="135"/>
@@ -20146,28 +20146,28 @@
       <c r="N548" s="135"/>
       <c r="O548" s="138"/>
     </row>
-    <row r="549" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="125"/>
-      <c r="B549" s="248" t="s">
+      <c r="B549" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C549" s="248"/>
-      <c r="D549" s="248"/>
-      <c r="E549" s="248"/>
-      <c r="F549" s="248"/>
-      <c r="G549" s="248"/>
+      <c r="C549" s="247"/>
+      <c r="D549" s="247"/>
+      <c r="E549" s="247"/>
+      <c r="F549" s="247"/>
+      <c r="G549" s="247"/>
       <c r="H549" s="127"/>
       <c r="I549" s="127"/>
-      <c r="J549" s="248" t="s">
+      <c r="J549" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K549" s="248"/>
-      <c r="L549" s="248"/>
-      <c r="M549" s="248"/>
-      <c r="N549" s="248"/>
-      <c r="O549" s="248"/>
-    </row>
-    <row r="550" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K549" s="247"/>
+      <c r="L549" s="247"/>
+      <c r="M549" s="247"/>
+      <c r="N549" s="247"/>
+      <c r="O549" s="247"/>
+    </row>
+    <row r="550" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="125"/>
       <c r="B550" s="126"/>
       <c r="C550" s="128"/>
@@ -20184,28 +20184,28 @@
       <c r="N550" s="128"/>
       <c r="O550" s="128"/>
     </row>
-    <row r="551" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="125"/>
-      <c r="B551" s="247" t="s">
+      <c r="B551" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C551" s="247"/>
-      <c r="D551" s="247"/>
-      <c r="E551" s="247"/>
-      <c r="F551" s="247"/>
-      <c r="G551" s="247"/>
+      <c r="C551" s="248"/>
+      <c r="D551" s="248"/>
+      <c r="E551" s="248"/>
+      <c r="F551" s="248"/>
+      <c r="G551" s="248"/>
       <c r="H551" s="129"/>
       <c r="I551" s="130"/>
-      <c r="J551" s="247" t="s">
+      <c r="J551" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K551" s="247"/>
-      <c r="L551" s="247"/>
-      <c r="M551" s="247"/>
-      <c r="N551" s="247"/>
-      <c r="O551" s="247"/>
-    </row>
-    <row r="552" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K551" s="248"/>
+      <c r="L551" s="248"/>
+      <c r="M551" s="248"/>
+      <c r="N551" s="248"/>
+      <c r="O551" s="248"/>
+    </row>
+    <row r="552" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="125"/>
       <c r="B552" s="131">
         <f>+B523+1</f>
@@ -20227,7 +20227,7 @@
       <c r="N552" s="132"/>
       <c r="O552" s="132"/>
     </row>
-    <row r="553" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="125"/>
       <c r="B553" s="133" t="s">
         <v>93</v>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="O553" s="136"/>
     </row>
-    <row r="554" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="125"/>
       <c r="B554" s="133" t="s">
         <v>94</v>
@@ -20285,7 +20285,7 @@
       <c r="M554" s="135"/>
       <c r="O554" s="135"/>
     </row>
-    <row r="555" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="125"/>
       <c r="B555" s="133" t="s">
         <v>95</v>
@@ -20312,7 +20312,7 @@
       <c r="N555" s="135"/>
       <c r="O555" s="135"/>
     </row>
-    <row r="556" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="125"/>
       <c r="B556" s="133"/>
       <c r="C556" s="135"/>
@@ -20329,7 +20329,7 @@
       <c r="N556" s="135"/>
       <c r="O556" s="135"/>
     </row>
-    <row r="557" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="125"/>
       <c r="B557" s="133" t="s">
         <v>96</v>
@@ -20356,7 +20356,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="558" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="125"/>
       <c r="B558" s="133" t="s">
         <v>97</v>
@@ -20383,7 +20383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="125"/>
       <c r="B559" s="133" t="s">
         <v>98</v>
@@ -20409,7 +20409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="125"/>
       <c r="B560" s="133" t="s">
         <v>99</v>
@@ -20434,7 +20434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="125"/>
       <c r="B561" s="135"/>
       <c r="C561" s="135"/>
@@ -20461,7 +20461,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="562" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="125"/>
       <c r="B562" s="135"/>
       <c r="C562" s="135"/>
@@ -20478,7 +20478,7 @@
       <c r="N562" s="135"/>
       <c r="O562" s="138"/>
     </row>
-    <row r="563" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="125"/>
       <c r="B563" s="135"/>
       <c r="C563" s="133" t="s">
@@ -20498,7 +20498,7 @@
       <c r="N563" s="135"/>
       <c r="O563" s="138"/>
     </row>
-    <row r="564" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="125"/>
       <c r="B564" s="135"/>
       <c r="C564" s="135"/>
@@ -20524,7 +20524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="125"/>
       <c r="B565" s="135"/>
       <c r="C565" s="135"/>
@@ -20550,7 +20550,7 @@
         <v>426.75000000000006</v>
       </c>
     </row>
-    <row r="566" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="125"/>
       <c r="B566" s="135"/>
       <c r="C566" s="135"/>
@@ -20576,7 +20576,7 @@
         <v>142.25000000000003</v>
       </c>
     </row>
-    <row r="567" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="125"/>
       <c r="B567" s="135"/>
       <c r="C567" s="135"/>
@@ -20599,7 +20599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="125"/>
       <c r="B568" s="135"/>
       <c r="C568" s="135"/>
@@ -20622,7 +20622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="125"/>
       <c r="B569" s="135"/>
       <c r="C569" s="135"/>
@@ -20645,7 +20645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="125"/>
       <c r="B570" s="135"/>
       <c r="C570" s="135"/>
@@ -20672,7 +20672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="125"/>
       <c r="B571" s="135"/>
       <c r="C571" s="135"/>
@@ -20698,7 +20698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="125"/>
       <c r="B572" s="135"/>
       <c r="C572" s="135"/>
@@ -20725,7 +20725,7 @@
         <v>569.00000000000011</v>
       </c>
     </row>
-    <row r="573" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="125"/>
       <c r="B573" s="135"/>
       <c r="C573" s="135"/>
@@ -20742,7 +20742,7 @@
       <c r="N573" s="135"/>
       <c r="O573" s="138"/>
     </row>
-    <row r="574" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="125"/>
       <c r="B574" s="135"/>
       <c r="C574" s="133" t="s">
@@ -20769,7 +20769,7 @@
         <v>13656.000000000002</v>
       </c>
     </row>
-    <row r="575" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="125"/>
       <c r="B575" s="135"/>
       <c r="C575" s="133"/>
@@ -20786,7 +20786,7 @@
       <c r="N575" s="135"/>
       <c r="O575" s="138"/>
     </row>
-    <row r="576" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="125"/>
       <c r="B576" s="135"/>
       <c r="C576" s="135"/>
@@ -20803,7 +20803,7 @@
       <c r="N576" s="135"/>
       <c r="O576" s="138"/>
     </row>
-    <row r="577" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="125"/>
       <c r="B577" s="135"/>
       <c r="C577" s="135"/>
@@ -20824,28 +20824,28 @@
       <c r="N577" s="135"/>
       <c r="O577" s="138"/>
     </row>
-    <row r="578" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="125"/>
-      <c r="B578" s="248" t="s">
+      <c r="B578" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="C578" s="248"/>
-      <c r="D578" s="248"/>
-      <c r="E578" s="248"/>
-      <c r="F578" s="248"/>
-      <c r="G578" s="248"/>
+      <c r="C578" s="247"/>
+      <c r="D578" s="247"/>
+      <c r="E578" s="247"/>
+      <c r="F578" s="247"/>
+      <c r="G578" s="247"/>
       <c r="H578" s="127"/>
       <c r="I578" s="127"/>
-      <c r="J578" s="248" t="s">
+      <c r="J578" s="247" t="s">
         <v>91</v>
       </c>
-      <c r="K578" s="248"/>
-      <c r="L578" s="248"/>
-      <c r="M578" s="248"/>
-      <c r="N578" s="248"/>
-      <c r="O578" s="248"/>
-    </row>
-    <row r="579" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K578" s="247"/>
+      <c r="L578" s="247"/>
+      <c r="M578" s="247"/>
+      <c r="N578" s="247"/>
+      <c r="O578" s="247"/>
+    </row>
+    <row r="579" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="125"/>
       <c r="B579" s="126"/>
       <c r="C579" s="128"/>
@@ -20862,28 +20862,28 @@
       <c r="N579" s="128"/>
       <c r="O579" s="128"/>
     </row>
-    <row r="580" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="125"/>
-      <c r="B580" s="247" t="s">
+      <c r="B580" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="C580" s="247"/>
-      <c r="D580" s="247"/>
-      <c r="E580" s="247"/>
-      <c r="F580" s="247"/>
-      <c r="G580" s="247"/>
+      <c r="C580" s="248"/>
+      <c r="D580" s="248"/>
+      <c r="E580" s="248"/>
+      <c r="F580" s="248"/>
+      <c r="G580" s="248"/>
       <c r="H580" s="129"/>
       <c r="I580" s="130"/>
-      <c r="J580" s="247" t="s">
+      <c r="J580" s="248" t="s">
         <v>92</v>
       </c>
-      <c r="K580" s="247"/>
-      <c r="L580" s="247"/>
-      <c r="M580" s="247"/>
-      <c r="N580" s="247"/>
-      <c r="O580" s="247"/>
-    </row>
-    <row r="581" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K580" s="248"/>
+      <c r="L580" s="248"/>
+      <c r="M580" s="248"/>
+      <c r="N580" s="248"/>
+      <c r="O580" s="248"/>
+    </row>
+    <row r="581" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="125"/>
       <c r="B581" s="131">
         <f>+B552+1</f>
@@ -20905,7 +20905,7 @@
       <c r="N581" s="132"/>
       <c r="O581" s="132"/>
     </row>
-    <row r="582" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="125"/>
       <c r="B582" s="133" t="s">
         <v>93</v>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="O582" s="136"/>
     </row>
-    <row r="583" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="125"/>
       <c r="B583" s="133" t="s">
         <v>94</v>
@@ -20963,7 +20963,7 @@
       <c r="M583" s="135"/>
       <c r="O583" s="135"/>
     </row>
-    <row r="584" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="125"/>
       <c r="B584" s="133" t="s">
         <v>95</v>
@@ -20990,7 +20990,7 @@
       <c r="N584" s="135"/>
       <c r="O584" s="135"/>
     </row>
-    <row r="585" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="125"/>
       <c r="B585" s="133"/>
       <c r="C585" s="135"/>
@@ -21007,7 +21007,7 @@
       <c r="N585" s="135"/>
       <c r="O585" s="135"/>
     </row>
-    <row r="586" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="125"/>
       <c r="B586" s="133" t="s">
         <v>96</v>
@@ -21034,7 +21034,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="587" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="125"/>
       <c r="B587" s="133" t="s">
         <v>97</v>
@@ -21061,7 +21061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="125"/>
       <c r="B588" s="133" t="s">
         <v>98</v>
@@ -21087,7 +21087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="125"/>
       <c r="B589" s="133" t="s">
         <v>99</v>
@@ -21112,7 +21112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="125"/>
       <c r="B590" s="135"/>
       <c r="C590" s="135"/>
@@ -21139,7 +21139,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="591" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="125"/>
       <c r="B591" s="135"/>
       <c r="C591" s="135"/>
@@ -21156,7 +21156,7 @@
       <c r="N591" s="135"/>
       <c r="O591" s="138"/>
     </row>
-    <row r="592" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="125"/>
       <c r="B592" s="135"/>
       <c r="C592" s="133" t="s">
@@ -21176,7 +21176,7 @@
       <c r="N592" s="135"/>
       <c r="O592" s="138"/>
     </row>
-    <row r="593" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="125"/>
       <c r="B593" s="135"/>
       <c r="C593" s="135"/>
@@ -21202,7 +21202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="125"/>
       <c r="B594" s="135"/>
       <c r="C594" s="135"/>
@@ -21228,7 +21228,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="125"/>
       <c r="B595" s="135"/>
       <c r="C595" s="135"/>
@@ -21254,7 +21254,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="125"/>
       <c r="B596" s="135"/>
       <c r="C596" s="135"/>
@@ -21277,7 +21277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="125"/>
       <c r="B597" s="135"/>
       <c r="C597" s="135"/>
@@ -21300,7 +21300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="125"/>
       <c r="B598" s="135"/>
       <c r="C598" s="135"/>
@@ -21323,7 +21323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="125"/>
       <c r="B599" s="135"/>
       <c r="C599" s="135"/>
@@ -21350,7 +21350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="125"/>
       <c r="B600" s="135"/>
       <c r="C600" s="135"/>
@@ -21376,7 +21376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="125"/>
       <c r="B601" s="135"/>
       <c r="C601" s="135"/>
@@ -21403,7 +21403,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="125"/>
       <c r="B602" s="135"/>
       <c r="C602" s="135"/>
@@ -21420,7 +21420,7 @@
       <c r="N602" s="135"/>
       <c r="O602" s="138"/>
     </row>
-    <row r="603" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A603" s="125"/>
       <c r="B603" s="135"/>
       <c r="C603" s="133" t="s">
@@ -21447,7 +21447,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A604" s="125"/>
       <c r="B604" s="135"/>
       <c r="C604" s="133"/>
@@ -21464,7 +21464,7 @@
       <c r="N604" s="135"/>
       <c r="O604" s="138"/>
     </row>
-    <row r="605" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="125"/>
       <c r="B605" s="135"/>
       <c r="C605" s="135"/>
@@ -21481,7 +21481,7 @@
       <c r="N605" s="135"/>
       <c r="O605" s="138"/>
     </row>
-    <row r="606" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="125"/>
       <c r="B606" s="135"/>
       <c r="C606" s="135"/>
@@ -21504,6 +21504,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="B522:G522"/>
+    <mergeCell ref="J522:O522"/>
+    <mergeCell ref="B549:G549"/>
+    <mergeCell ref="J549:O549"/>
+    <mergeCell ref="B551:G551"/>
+    <mergeCell ref="J551:O551"/>
+    <mergeCell ref="B520:G520"/>
+    <mergeCell ref="J520:O520"/>
+    <mergeCell ref="B493:G493"/>
+    <mergeCell ref="J493:O493"/>
+    <mergeCell ref="B462:G462"/>
+    <mergeCell ref="J462:O462"/>
+    <mergeCell ref="B464:G464"/>
+    <mergeCell ref="J464:O464"/>
+    <mergeCell ref="B491:G491"/>
+    <mergeCell ref="J491:O491"/>
+    <mergeCell ref="B434:G434"/>
+    <mergeCell ref="J434:O434"/>
+    <mergeCell ref="B436:G436"/>
+    <mergeCell ref="J436:O436"/>
+    <mergeCell ref="B376:G376"/>
+    <mergeCell ref="J376:O376"/>
+    <mergeCell ref="B378:G378"/>
+    <mergeCell ref="J378:O378"/>
+    <mergeCell ref="B405:G405"/>
+    <mergeCell ref="J405:O405"/>
+    <mergeCell ref="B407:G407"/>
+    <mergeCell ref="J407:O407"/>
+    <mergeCell ref="B320:G320"/>
+    <mergeCell ref="J320:O320"/>
+    <mergeCell ref="B347:G347"/>
+    <mergeCell ref="J347:O347"/>
+    <mergeCell ref="B349:G349"/>
+    <mergeCell ref="J349:O349"/>
+    <mergeCell ref="B289:G289"/>
+    <mergeCell ref="J289:O289"/>
+    <mergeCell ref="B291:G291"/>
+    <mergeCell ref="J291:O291"/>
+    <mergeCell ref="B318:G318"/>
+    <mergeCell ref="J318:O318"/>
+    <mergeCell ref="B233:G233"/>
+    <mergeCell ref="J233:O233"/>
+    <mergeCell ref="B260:G260"/>
+    <mergeCell ref="J260:O260"/>
+    <mergeCell ref="B262:G262"/>
+    <mergeCell ref="J262:O262"/>
+    <mergeCell ref="B173:G173"/>
+    <mergeCell ref="J173:O173"/>
+    <mergeCell ref="B175:G175"/>
+    <mergeCell ref="J175:O175"/>
+    <mergeCell ref="B231:G231"/>
+    <mergeCell ref="J231:O231"/>
+    <mergeCell ref="B202:G202"/>
+    <mergeCell ref="J202:O202"/>
+    <mergeCell ref="B204:G204"/>
+    <mergeCell ref="J204:O204"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="J118:O118"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="J145:O145"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="J147:O147"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="J88:O88"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="J90:O90"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="J116:O116"/>
     <mergeCell ref="B578:G578"/>
     <mergeCell ref="J578:O578"/>
     <mergeCell ref="B580:G580"/>
@@ -21520,74 +21588,6 @@
     <mergeCell ref="J59:O59"/>
     <mergeCell ref="B61:G61"/>
     <mergeCell ref="J61:O61"/>
-    <mergeCell ref="B88:G88"/>
-    <mergeCell ref="J88:O88"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="J90:O90"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="J116:O116"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="J118:O118"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="J145:O145"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="J147:O147"/>
-    <mergeCell ref="B173:G173"/>
-    <mergeCell ref="J173:O173"/>
-    <mergeCell ref="B175:G175"/>
-    <mergeCell ref="J175:O175"/>
-    <mergeCell ref="B231:G231"/>
-    <mergeCell ref="J231:O231"/>
-    <mergeCell ref="B202:G202"/>
-    <mergeCell ref="J202:O202"/>
-    <mergeCell ref="B204:G204"/>
-    <mergeCell ref="J204:O204"/>
-    <mergeCell ref="B233:G233"/>
-    <mergeCell ref="J233:O233"/>
-    <mergeCell ref="B260:G260"/>
-    <mergeCell ref="J260:O260"/>
-    <mergeCell ref="B262:G262"/>
-    <mergeCell ref="J262:O262"/>
-    <mergeCell ref="B289:G289"/>
-    <mergeCell ref="J289:O289"/>
-    <mergeCell ref="B291:G291"/>
-    <mergeCell ref="J291:O291"/>
-    <mergeCell ref="B318:G318"/>
-    <mergeCell ref="J318:O318"/>
-    <mergeCell ref="B320:G320"/>
-    <mergeCell ref="J320:O320"/>
-    <mergeCell ref="B347:G347"/>
-    <mergeCell ref="J347:O347"/>
-    <mergeCell ref="B349:G349"/>
-    <mergeCell ref="J349:O349"/>
-    <mergeCell ref="B434:G434"/>
-    <mergeCell ref="J434:O434"/>
-    <mergeCell ref="B436:G436"/>
-    <mergeCell ref="J436:O436"/>
-    <mergeCell ref="B376:G376"/>
-    <mergeCell ref="J376:O376"/>
-    <mergeCell ref="B378:G378"/>
-    <mergeCell ref="J378:O378"/>
-    <mergeCell ref="B405:G405"/>
-    <mergeCell ref="J405:O405"/>
-    <mergeCell ref="B407:G407"/>
-    <mergeCell ref="J407:O407"/>
-    <mergeCell ref="B520:G520"/>
-    <mergeCell ref="J520:O520"/>
-    <mergeCell ref="B493:G493"/>
-    <mergeCell ref="J493:O493"/>
-    <mergeCell ref="B462:G462"/>
-    <mergeCell ref="J462:O462"/>
-    <mergeCell ref="B464:G464"/>
-    <mergeCell ref="J464:O464"/>
-    <mergeCell ref="B491:G491"/>
-    <mergeCell ref="J491:O491"/>
-    <mergeCell ref="B522:G522"/>
-    <mergeCell ref="J522:O522"/>
-    <mergeCell ref="B549:G549"/>
-    <mergeCell ref="J549:O549"/>
-    <mergeCell ref="B551:G551"/>
-    <mergeCell ref="J551:O551"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
